--- a/Question_Classification/results/expert_review/reviewer_discordances.xlsx
+++ b/Question_Classification/results/expert_review/reviewer_discordances.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="556">
   <si>
     <t>Year</t>
   </si>
@@ -49,21 +49,84 @@
     <t>Reviewer 2 Primary</t>
   </si>
   <si>
+    <t>ssm20174</t>
+  </si>
+  <si>
     <t>ssm201715</t>
   </si>
   <si>
+    <t>ssm201734</t>
+  </si>
+  <si>
+    <t>ssm201738</t>
+  </si>
+  <si>
+    <t>ssm201777</t>
+  </si>
+  <si>
     <t>ssm201783</t>
   </si>
   <si>
     <t>ssm2017142</t>
   </si>
   <si>
+    <t>ssm2017188</t>
+  </si>
+  <si>
+    <t>ssm2017208</t>
+  </si>
+  <si>
+    <t>ssm2017223</t>
+  </si>
+  <si>
+    <t>ssm2017225</t>
+  </si>
+  <si>
+    <t>ssm2017233</t>
+  </si>
+  <si>
+    <t>ssm2017238</t>
+  </si>
+  <si>
+    <t>ssm2017239</t>
+  </si>
+  <si>
+    <t>ssm2017240</t>
+  </si>
+  <si>
+    <t>ssm2017251</t>
+  </si>
+  <si>
+    <t>ssm2017267</t>
+  </si>
+  <si>
+    <t>ssm2017276</t>
+  </si>
+  <si>
+    <t>ssm20182142154</t>
+  </si>
+  <si>
+    <t>ssm20182142354</t>
+  </si>
+  <si>
+    <t>ssm20182142404</t>
+  </si>
+  <si>
     <t>ssm20182142504</t>
   </si>
   <si>
     <t>ssm20182142554</t>
   </si>
   <si>
+    <t>ssm20182143654</t>
+  </si>
+  <si>
+    <t>ssm20182144004</t>
+  </si>
+  <si>
+    <t>ssm20182144154</t>
+  </si>
+  <si>
     <t>ssm20182144454</t>
   </si>
   <si>
@@ -82,6 +145,9 @@
     <t>ssm20182145554</t>
   </si>
   <si>
+    <t>ssm20182145754</t>
+  </si>
+  <si>
     <t>ssm20182145904</t>
   </si>
   <si>
@@ -91,9 +157,18 @@
     <t>ssm20182146104</t>
   </si>
   <si>
+    <t>ssm20182146404</t>
+  </si>
+  <si>
+    <t>ssm20182147404</t>
+  </si>
+  <si>
     <t>ssm20182147454</t>
   </si>
   <si>
+    <t>ssm20182147704</t>
+  </si>
+  <si>
     <t>ssm20182147854</t>
   </si>
   <si>
@@ -109,12 +184,27 @@
     <t>ssm20182148354</t>
   </si>
   <si>
+    <t>ssm20182148404</t>
+  </si>
+  <si>
+    <t>ssm20182148804</t>
+  </si>
+  <si>
     <t>ssm20203813204</t>
   </si>
   <si>
+    <t>ssm20203814854</t>
+  </si>
+  <si>
     <t>ssm20203814904</t>
   </si>
   <si>
+    <t>ssm20203816654</t>
+  </si>
+  <si>
+    <t>ssm20203816954</t>
+  </si>
+  <si>
     <t>ssm202110228904</t>
   </si>
   <si>
@@ -130,42 +220,141 @@
     <t>ssm202110230754</t>
   </si>
   <si>
+    <t>ssm202110231654</t>
+  </si>
+  <si>
+    <t>ssm202110232254</t>
+  </si>
+  <si>
+    <t>ssm202110232504</t>
+  </si>
+  <si>
+    <t>ssm202110232904</t>
+  </si>
+  <si>
+    <t>ssm202110234704</t>
+  </si>
+  <si>
     <t>ssm202110234854</t>
   </si>
   <si>
+    <t>ssm202110234904</t>
+  </si>
+  <si>
+    <t>ssm202110234954</t>
+  </si>
+  <si>
     <t>ssm202110235054</t>
   </si>
   <si>
+    <t>ssm202110235504</t>
+  </si>
+  <si>
+    <t>ssm202110235654</t>
+  </si>
+  <si>
+    <t>ssm202110235704</t>
+  </si>
+  <si>
     <t>ssm2022152</t>
   </si>
   <si>
+    <t>ssm2022156</t>
+  </si>
+  <si>
     <t>ssm2022173</t>
   </si>
   <si>
+    <t>ssm2022175</t>
+  </si>
+  <si>
+    <t>ssm2022180</t>
+  </si>
+  <si>
     <t>ssm2022181</t>
   </si>
   <si>
+    <t>ssm2022185</t>
+  </si>
+  <si>
+    <t>ssm2022186</t>
+  </si>
+  <si>
+    <t>ssm2022191</t>
+  </si>
+  <si>
+    <t>ssm2022193</t>
+  </si>
+  <si>
+    <t>ssm2022195</t>
+  </si>
+  <si>
+    <t>ssm2022199</t>
+  </si>
+  <si>
     <t>ssm2022213</t>
   </si>
   <si>
+    <t>ssm2022224</t>
+  </si>
+  <si>
+    <t>ssm2022231</t>
+  </si>
+  <si>
+    <t>ssm2022239</t>
+  </si>
+  <si>
+    <t>ssm2022240</t>
+  </si>
+  <si>
     <t>ssm2022242</t>
   </si>
   <si>
+    <t>ssm2022243</t>
+  </si>
+  <si>
     <t>ssm2022245</t>
   </si>
   <si>
+    <t>ssm2022251</t>
+  </si>
+  <si>
+    <t>ssm2022268</t>
+  </si>
+  <si>
+    <t>ssm2022271</t>
+  </si>
+  <si>
     <t>ssm2022278</t>
   </si>
   <si>
     <t>ssm2023446</t>
   </si>
   <si>
+    <t>ssm2023449</t>
+  </si>
+  <si>
+    <t>ssm2023451</t>
+  </si>
+  <si>
+    <t>ssm2023455</t>
+  </si>
+  <si>
     <t>ssm2023456</t>
   </si>
   <si>
     <t>ssm2023462</t>
   </si>
   <si>
+    <t>ssm2023463</t>
+  </si>
+  <si>
+    <t>ssm2023466</t>
+  </si>
+  <si>
+    <t>ssm2023488</t>
+  </si>
+  <si>
     <t>ssm2023491</t>
   </si>
   <si>
@@ -175,12 +364,27 @@
     <t>ssm2023520</t>
   </si>
   <si>
+    <t>ssm2023533</t>
+  </si>
+  <si>
     <t>ssm2023546</t>
   </si>
   <si>
     <t>ssm2023547</t>
   </si>
   <si>
+    <t>ssm2023548</t>
+  </si>
+  <si>
+    <t>ssm2023551</t>
+  </si>
+  <si>
+    <t>ssm2023554</t>
+  </si>
+  <si>
+    <t>ssm2023557</t>
+  </si>
+  <si>
     <t>ssm2023560</t>
   </si>
   <si>
@@ -193,33 +397,114 @@
     <t>ssm2023681</t>
   </si>
   <si>
+    <t>ssm2023685</t>
+  </si>
+  <si>
+    <t>ssm2023692</t>
+  </si>
+  <si>
+    <t>ssm2023693</t>
+  </si>
+  <si>
     <t>ssm2023711</t>
   </si>
   <si>
+    <t>ssm2023719</t>
+  </si>
+  <si>
     <t>ssm2025862</t>
   </si>
   <si>
     <t>ssm2025864</t>
   </si>
   <si>
+    <t>ssm2025867</t>
+  </si>
+  <si>
     <t>ssm2025868</t>
   </si>
   <si>
+    <t>ssm2025920</t>
+  </si>
+  <si>
+    <t>Quale delle seguenti è una traslocazione tipicamente associata al sarcoma di Ewing?</t>
+  </si>
+  <si>
     <t>Una ragazza di 15 anni si presenta in Pronto Soccorso perché da un'ora ha difficoltà respiratoria, frequenza respiratoria 35 atti/min e all'auscultazione apprezzate fischi e sibili. Raccogliendo l'anamnesi quale informazione clinica più probabilmente emergerà?</t>
   </si>
   <si>
+    <t>Un paziente esegue una TC del torace che dimostra un nodulo subpleurico del lobo superiore sinistro a margini spiculati di diametro 1,8 cm. Nel sospetto di neoplasia polmonare, quale tra i seguenti è l'esame diagnostico più appropriato per la stadiazione della malattia, in funzione della pianificazione della strategia terapeutica?</t>
+  </si>
+  <si>
+    <t>Un paziente di 54 anni lamenta da 3 mesi violento dolore anale, scatenato dalla defecazione, ma perdurante per diverse ore. A volte ha proctorragie di modesta entità. A quale esame deve essere sottoposto il paziente in prima istanza per confermare il sospetto diagnostico?</t>
+  </si>
+  <si>
+    <t>L'uso di quale dei seguenti farmaci comporta un maggior rischio di ulcera gastrica?</t>
+  </si>
+  <si>
     <t>Una ragazza di 15 anni viene portata dai genitori dalla ginecologa per amenorrea. Presenta anche un limitato sviluppo puberale associato a bassa statura, torace a scudo e bassa attaccatura dei capelli. L'esame ecografico transvaginale mostra la presenza di banderelle fibrose al posto delle ovaie. Qual è la diagnosi più probabile?</t>
   </si>
   <si>
     <t>Un paziente noto per TVP recidivanti lamenta improvvisa difficoltà respiratoria. In considerazione dell'anamnesi remota e della sintomatologia suggestiva per embolia polmonare, quale delle seguenti condizioni aumenta maggiormente la probabilità di tale diagnosi?</t>
   </si>
   <si>
+    <t>Un ragazzo di 23 anni è vittima di un incidente automobilistico (moto contro auto). All'arrivo dei soccorsi viene riferito il seguente esame obiettivo neurologico: il paziente giace a occhi chiusi, non li apre né allo stimolo verbale né allo stimolo doloroso, eloquio assente, alla stimolazione algica il paziente tende ad allontanare gli arti dalla fonte dello stimolo. Presenta anisocoria per destra &gt; sinistra. Qual è il valore della Glasgow Coma Scale di questo paziente?</t>
+  </si>
+  <si>
+    <t>Un uomo di 69 anni, portatore di microcitoma polmonare con secondarismi epatici, lamenta da circa 7 giorni cefalea, episodi di vertigini e diplopia. Considerati l'anamnesi e i sintomi presentati, quale potrebbe essere l'esame diagnostico di scelta in questa condizione?</t>
+  </si>
+  <si>
+    <t>Ragazzo di 17 anni, giunge per ostruzione respiratoria nasale bilaterale insorta nella stagione primaverile, rinorrea sierosa, iperemia congiuntivale e iposmia. Riferisce analoga sintomatologia un anno prima, risoltasi poi spontaneamente durante il periodo estivo. Quale diagnosi è più probabile?</t>
+  </si>
+  <si>
+    <t>Ragazzo di 17 anni, giunge per ostruzione respiratoria nasale bilaterale insorta nella stagione primaverile, rinorrea sierosa, iperemia congiuntivale e iposmia. Riferisce analoga sintomatologia un anno prima, risoltasi poi spontaneamente durante il periodo estivo. Quale trattamento è opportuno consigliare?</t>
+  </si>
+  <si>
+    <t>Quale delle seguenti affermazioni, per quanto riguarda la bassa statura familiare, è ERRATA?</t>
+  </si>
+  <si>
+    <t>Bambina di 18 mesi, giunge in Pronto Soccorso per caduta accidentale dal divano di casa, in seguito alla quale ha riportato trauma temporale sinistro, senza perdita di coscienza. All'arrivo in PS la bambina si presenta in buone condizioni generali, vispa, reattiva e neurologicamente indenne. All'esame clinico si evidenzia solo un ematoma sottogaleale in sede di trauma. In caso di comparsa di sintomi neurologici, quale dei seguenti esami è il più indicato?</t>
+  </si>
+  <si>
+    <t>Bambino di cinque mesi, unicogenito nato a termine, dopo gravidanza normodecorsa. Crescita regolare. Allattamento materno. Non problemi perinatali. Da qualche giorno presenta febbre (39 °C), inappetenza e qualche episodio di vomito. Il pediatra prescrive un'urinocoltura. Quale delle seguenti affermazioni NON è corretta?</t>
+  </si>
+  <si>
+    <t>Bambino di cinque mesi, unicogenito nato a termine, dopo gravidanza normodecorsa. Crescita regolare. Allattamento materno. Non problemi perinatali. Da qualche giorno presenta febbre (39 °C), inappetenza e qualche episodio di vomito. Il pediatra prescrive un'urinocoltura. In caso di urinocoltura positiva, la terapia antibiotica deve essere somministrata per via parenterale</t>
+  </si>
+  <si>
+    <t>Uomo di 35 anni, seguito dai servizi territoriali da 10 anni, giunge in Pronto Soccorso accompagnato dai genitori per riacutizzazione da circa una settimana del quadro clinico con comparsa di ritiro sociale, anoressia, delirio di tipo persecutorio incentrato sui colleghi, dispercezioni uditive di tipo imperativo. La mimica appare fatua, dissintona, eloquio da stimolare, tono dell'umore appiattito. Il sonno viene descritto come regolare. Nel caso di scarsa aderenza ai trattamenti farmacologici orali, quale strategia terapeutica è più opportuna per la prevenzione delle ricadute?</t>
+  </si>
+  <si>
+    <t>Un uomo di 56 anni giunge all'attenzione medica riferendo comparsa nella notte di intenso dolore a livello del ginocchio destro. Ha assunto paracetamolo 1 grammo, con scarso beneficio. Si sospetta artropatia da cristalli. Si pone diagnosi di artrite gottosa e viene avviata un'appropriata terapia. Dopo 3 giorni di terapia il paziente riferisce comparsa di importante diarrea. Quale dei seguenti farmaci comunemente utilizzati nella terapia dell'artrite gottosa si associa più comunemente a tale effetto collaterale?</t>
+  </si>
+  <si>
+    <t>Una donna di 36 anni si reca in Pronto Soccorso lamentando un forte dolore al fianco sinistro, irradiato all'inguine. In sala di attesa comincia ad avere brividi e febbre. Quale tipo di calcoli NON è visibile a un RX addome?</t>
+  </si>
+  <si>
+    <t>Il trattamento di prima linea (il più importante da somministrare) dello shock anafilattico prevede somministrazione di</t>
+  </si>
+  <si>
+    <t>Un paziente deve essere sottoposto a un intervento chirurgico ortopedico. Subito dopo l'esecuzione dell'anestesia locoregionale, il paziente sviluppa i sintomi di tossicità sistemica da anestetico locale. Qual è l'antidoto da somministrare?</t>
+  </si>
+  <si>
+    <t>Una donna di 45 anni giunge al Pronto Soccorso in coma e depressione respiratoria, il medico somministra naloxone cloridrato 0,4 mg per via endovenosa. Il naloxone cloridrato è</t>
+  </si>
+  <si>
     <t>Il diverticolo di Meckel è</t>
   </si>
   <si>
     <t>Una donna di 39 anni riferisce da circa tre mesi dolore anale violento scatenato dalla defecazione con episodi di sanguinamento. Qual è la diagnosi più probabile?</t>
   </si>
   <si>
+    <t>Un paziente affetto da emicrania senza aura si rivolge a un neurologo per decidere la terapia più appropriata. Quale, tra i seguenti farmaci, rientra tra quelli da utilizzare durante l'attacco acuto dell'emicrania?</t>
+  </si>
+  <si>
+    <t>Quale delle seguenti NON è considerata un'infezione sessualmente trasmessa?</t>
+  </si>
+  <si>
+    <t>Una donna di 37 anni, all'ottava settimana di gravidanza, ai primi esami presenta Hb 9,5 g/dL e MCV 72 fl. Quale di queste condizioni NON può essere la causa dei valori presentati nello scenario?</t>
+  </si>
+  <si>
     <t>La legge istitutiva del Sistema Sanitario Nazionale è</t>
   </si>
   <si>
@@ -238,6 +523,9 @@
     <t>Un uomo ha lavorato in falegnameria come carteggiatore per circa 40 anni. Riferisce che l'ambiente di lavoro era estremamente polveroso. L'uomo lamenta epistassi ricorrenti. Quale delle seguenti patologie può essere maggiormente correlata all'anamnesi lavorativa del paziente?</t>
   </si>
   <si>
+    <t>Un uomo di 66 anni, obeso, fumatore e iperteso, è in terapia con simvastatina (40 mg) da circa 2 anni dopo un grave infarto del miocardio. A una visita di controllo i valori plasmatici di trigliceridi risultano accettabili, mentre quelli del colesterolo LDL risultano eccessivamente elevati rispetto agli obiettivi terapeutici. Quale dei seguenti farmaci è la migliore associazione alla simvastatina in modo da ottenere un'ulteriore riduzione dei valori di LDL, garantendo una buona sicurezza terapeutica?</t>
+  </si>
+  <si>
     <t>Una donna di 64 anni, nota per cardiopatia ipertensiva, si presenta in Pronto Soccorso lamentando debolezza muscolare e palpitazioni. L'ECG mostra onde T appuntite ("a tenda") e un intervallo PR prolungato. Quale dei seguenti farmaci è verosimilmente responsabile dei sintomi della paziente e del quadro ECG descritto?</t>
   </si>
   <si>
@@ -247,9 +535,18 @@
     <t>Una donna di 45 anni riferisce ematuria e dolore al fianco destro da qualche settimana. Le sembra anche di avvertire una massa palpabile a livello del fianco destro. Si pone il sospetto di una neoplasia del rene. Qual è il primo esame diagnostico che si dovrebbe proporre?</t>
   </si>
   <si>
+    <t>Una ragazza di 20 anni si rivolge al proprio medico curante per febbre, malessere e dolore urente in sede genitale. Alla visita vengono riscontrati una linfoadenopatia inguinale dolente, lesioni vescicolari ed erosioni a livello dei genitali esterni. Qual è l'agente eziologico verosimilmente responsabile di tale infezione genitale?</t>
+  </si>
+  <si>
+    <t>Una donna di 45 anni giunge in Pronto Soccorso per comparsa di paresi facciale destra, dolore nevralgico mastoideo ed eruzione vescicolare a livello della conca e del condotto uditivo esterno destro. Quale quadro clinico si configura?</t>
+  </si>
+  <si>
     <t>Un bambino di 5 anni presenta una neoformazione della regione mediana del collo, non dolente, mobile con gli atti deglutitori, che ha presentato incremento volumetrico progressivo. Qual è la diagnosi più verosimile?</t>
   </si>
   <si>
+    <t>Una ragazza di 14 anni viene condotta all'attenzione medica per il presentarsi di ripetuti episodi di cefalea, di insorgenza variabile nel corso della giornata, in sede fronto-parietale monolaterale, di notevole intensità e di natura pulsante. Tali episodi si associano a fotofobia e nausea, l'esame obiettivo neurologico è negativo. Quale dei seguenti farmaci NON è indicato per il trattamento acuto di questa condizione?</t>
+  </si>
+  <si>
     <t>Un neonato di 22 giorni viene condotto in Pronto Soccorso perché da una settimana presenta vomiti alimentari ripetuti, non biliari, "a getto". Ha fame ed è calato di peso. Qual è la diagnosi più probabile?</t>
   </si>
   <si>
@@ -265,12 +562,27 @@
     <t>Indicare quale delle seguenti affermazioni sulle calcificazioni coronariche è ERRATA.</t>
   </si>
   <si>
+    <t>Una paziente di 69 anni, affetta da carcinoma della mammella, deve eseguire una scintigrafia ossea. Nella scintigrafia ossea, quali sono i radiofarmaci che vengono utilizzati di routine?</t>
+  </si>
+  <si>
+    <t>Perviene all'attenzione medica una ragazza di 17 anni, di normale peso e statura, che presenta sin dall'età infantile una litiasi renale recidivante; gli esami dimostrano: Creatininemia 0.8 mg/dL; Calcemia 9.3 mg/dL; Fosforemia 3.9 mg/dL; K+ 4.2 mEq/L; Uricemia 3.2 mg/dL; eccesso basi -0.8 mEq/L; PTH 32 pg/mL; Calciuria 140 mg/die; Uricuria 390 mg/die; Ossaluria 0.28 mmol/die; Citraturia 2.7 mmol/die; sedimento urinario che dimostra cristalli esagonali. Quale potrebbe essere una plausibile causa di questa forma di nefrolitiasi recidivante giovanile?</t>
+  </si>
+  <si>
     <t>Quale dei seguenti farmaci NON è indicato per la terapia dell'osteoporosi?</t>
   </si>
   <si>
+    <t>Il pediatra oncologo prescrive 3 L/m2/die di liquidi per via endovenosa a una bambina di 6 anni con nuova diagnosi di Leucemia Linfatica Acuta (LLA) per prevenire la sindrome da lisi tumorale, che può comportare severe complicanze metaboliche e idroelettrolitiche. Quale tra queste NON rientra tra le complicanze?</t>
+  </si>
+  <si>
     <t>Un bambino di 5 anni recentemente immigrato dal centro Africa giunge al Pronto Soccorso per dolore toracico acuto. Uno screening emato-biochimico mostra una modesta anemia macrocitica, iperbilirubinemia prevalentemente indiretta e aumento dell'LDH. L'ecocardiogramma è negativo, l'ecografia addominale mostra una milza di dimensioni diminuite. Quali delle seguenti condizioni dovrebbe essere sospettata?</t>
   </si>
   <si>
+    <t>In quale delle seguenti sindromi è più frequente la palatoschisi?</t>
+  </si>
+  <si>
+    <t>Quale dei seguenti tumori del testicolo origina da cellule "non germinali"?</t>
+  </si>
+  <si>
     <t>Un anziano viene ricoverato in pneumologia per il trattamento di una polmonite con piperacillina/tazobactam endovena. Dopo alcuni giorni compare diarrea non associata a febbre né a dolore addominale. Nel sospetto di una diarrea da Clostridium difficile, quale dei seguenti interventi è prioritario?</t>
   </si>
   <si>
@@ -286,42 +598,141 @@
     <t>Una donna di 38 anni, apparentemente sana, dopo un viaggio aereo Hong Kong - Roma in classe economica, all'arrivo in aeroporto sviluppa sincope seguita da dispnea con riscontro obiettivo di ipotensione. Portata subito al Pronto Soccorso dell'aeroporto, l'elettrocardiogramma mostra tachicardia sinusale, BBDx incompleto con onde T precordiali negative. Qual è la diagnosi più probabile?</t>
   </si>
   <si>
+    <t>Il sierogruppo di Neisseria meningitidis più frequentemente responsabile di malattia meningococcica invasiva nel primo anno di vita in Italia, negli ultimi anni (secondo il report epidemiologico sulle malattie batteriche invasive 2019 dell'Istituto Superiore di Sanità) è il</t>
+  </si>
+  <si>
+    <t>Un uomo di 32 anni lamenta, da alcune settimane, dolore anale violento post-defecatorio. Qual è la diagnosi più probabile?</t>
+  </si>
+  <si>
+    <t>Un uomo viene portato in Pronto Soccorso per estese ustioni di 2° e 3° grado. Secondo la regola del 9 di Wallace, a quale superficie di cute ustionata corrisponde un arto superiore?</t>
+  </si>
+  <si>
+    <t>Una ragazza di 22 anni presenta un'ulcera non dolente localizzata al grande labbro destro insorta qualche giorno prima. Clinicamente, qual è la diagnosi più probabile?</t>
+  </si>
+  <si>
+    <t>Una donna di 45 anni con storia di abuso di stupefacenti giunge al Pronto Soccorso in coma e depressione respiratoria; viene somministrato naloxone cloridrato 0,4 mg per via endovenosa in quanto</t>
+  </si>
+  <si>
     <t>Una donna è allettata per una frattura di femore destro. Durante il ricovero, in attesa di intervento, lamenta improvvisamente sensazione di mancanza d'aria e dolore toracico. Viene contattato l'ortopedico di guardia, che chiama il rianimatore, il quale la trova agitata, dispnoica e ipotesa. Il medico rianimatore prescrive immediatamente</t>
   </si>
   <si>
+    <t>Un uomo di 56 anni viene accompagnato in Pronto Soccorso dopo essere stato trovato incosciente a terra. Alla prima valutazione in sala emergenza egli apre gli occhi alla chiamata, localizza con gli arti lo stimolo doloroso ed emette dei lamenti. Qual è il suo punteggio di Glasgow Coma Scale (GCS)?</t>
+  </si>
+  <si>
+    <t>Un uomo di 47 anni, anamnesi muta, riferisce di avvertire "sapore metallico" in bocca qualche minuto dopo l'esecuzione di blocco interscalenico in vista di un intervento di artroscopia di spalla. Quale potrebbe essere la causa di questa condizione?</t>
+  </si>
+  <si>
     <t>In un paziente di 77 anni (in anamnesi cardiopatia ischemica rivascolarizzata tramite PTCA + stent qualche anno prima), ricoverato in rianimazione e sottoposto a ventilazione meccanica per shock settico ed insufficienza respiratoria, viene posizionato un catetere di Swan-Ganz come monitoraggio emodinamico invasivo. Pressione venosa centrale e Pressione di incuneamento risultano rispettivamente pari a 5 mmHg e 8 mmHg. Quale stato emodinamico si sospetta?</t>
   </si>
   <si>
+    <t>In relazione alla legge 833/78 istitutiva del SSN indicare quale delle seguenti affermazioni è FALSA</t>
+  </si>
+  <si>
+    <t>Un uomo di 70 anni, in gioventù, ha lavorato come coibentatore nella cantieristica navale e dieci anni or sono ha subito trattamento radioterapico per un linfoma a localizzazione mediastinica. Da alcuni mesi lamenta dispnea, astenia, febbricola e calo ponderale. L'RX del torace rivela un versamento pleurico sinistro. Sottoposto a toracoscopia, viene effettuato prelievo bioptico sulla pleura parietale. L'indagine istologica depone per un mesotelioma pleurico maligno. Quale tra questi fattori di rischio NON è correlato alla neoplasia?</t>
+  </si>
+  <si>
+    <t>Un dirigente medico in servizio da ormai 12 anni, quasi tutti i giorni, durante la pausa pranzo si reca presso la mensa della struttura ospedaliera di appartenenza. Stanco del solito menù, un giorno decide di pranzare presso un noto ristorante in centro città. Durante il tragitto in moto, egli viene però investito da un'automobile, riportando una frattura bi-ossea di gamba e alcune escoriazioni. A quale tipologia di indennizzo può accedere il medico, per l'evento occorsogli?</t>
+  </si>
+  <si>
     <t>Una donna di 60 anni a cui è stato recentemente prescritto un diuretico tiazidico, si presenta al Pronto Soccorso con affaticamento e palpitazioni. I suoi esami del sangue mostrano un potassio di 2,8 mEq/L. Nei pazienti con ipokaliemia significativa, quale altro elettrolita è generalmente basso?</t>
   </si>
   <si>
+    <t>Il paziente anziano che presenta una condizione di sarcopenia</t>
+  </si>
+  <si>
     <t>Quale delle seguenti classi di farmaci chemioterapici è maggiormente associata a cardiotossicità risultante in forma di disfunzione ventricolare sinistra?</t>
   </si>
   <si>
+    <t>Quale delle seguenti classi di farmaci trova un’indicazione per il trattamento sia del diabete mellito sia dello scompenso cardiaco a frazione di eiezione ridotta?</t>
+  </si>
+  <si>
+    <t>In una donna di 68 anni che si presenta con tosse persistente produttiva, quale tra le seguenti indagini diagnostiche è maggiormente indicata per confermare od escludere la presenza di bronchiectasie?</t>
+  </si>
+  <si>
     <t>Quale tra le seguenti è la causa più probabile di versamento pleurico bilaterale alla radiografia del torace in un paziente di sesso maschile di 70 anni che si presenta al Pronto Soccorso con dispnea cronica riacutizzata?</t>
   </si>
   <si>
+    <t>Paziente di 65 anni, nella storia clinica tabagismo, ipertensione arteriosa in trattamento con ACE-inibitori, diabete mellito in trattamento con metformina. Normofunzione renale, esame urine negativo. Accesso in Pronto Soccorso per sindrome coronarica acuta, si esegue coronarografia. Riscontro di stenosi critica delle arterie interventricolare anteriore e circonflessa. Si posizionano stent, inizia trattamento anti-aggregante. Al controllo dopo 10 giorni, riscontro di creatininemia di 3,5 mg/dl, eosinofilia, e lesioni violacee a carico degli arti inferiori. Qual è la diagnosi più probabile tra le seguenti?</t>
+  </si>
+  <si>
+    <t>Bracciante agricolo di 35 anni. Sostanziale benessere negli anni precedenti. Non fuma, saltuaria assunzione di superalcolici. Si presenta in Pronto Soccorso per comparsa da alcuni giorni di febbre, cefalea, ematuria, mialgie diffuse e dal giorno precedente riscontro di sclere itteriche. Da 48 ore oliguria. Nei giorni precedenti ha gestito irrigazione dei campi entrando in alcuni fossati per aprire le paratie senza indossare dispositivi di protezione individuali (gambali). Inizia terapia antibiotica e trattamento dialitico per 7 giorni, poi ripresa della funzione renale. Qual è la diagnosi più probabile tra le seguenti?</t>
+  </si>
+  <si>
+    <t>Un uomo di 40 anni effettua una valutazione neurologica su indicazione del Medico curante dal momento che, da alcuni mesi, ha iniziato a lamentare incertezza nella deambulazione (tende a sbattere spesso contro mobili o contro gli stipiti delle porte) associata a calo della libido e disfunzione erettile. All’esame obiettivo viene riscontrata ginecomastia, oltre ad un deficit campimetrico compatibile con emianopsia bitemporale. Quale tra le seguenti ipotesi appare più verosimile?</t>
+  </si>
+  <si>
+    <t>Un paziente affetto da depressione maggiore resistente nonostante una polifarmacoterapia ottimizzata manifesta ricorrenti ideazioni e tentativi suicidari. Quale dei seguenti farmaci risulta indicato?</t>
+  </si>
+  <si>
+    <t>Quale delle seguenti affermazioni relative all’atresia esofagea con fistola esofago-tracheale è ERRATA?</t>
+  </si>
+  <si>
+    <t>Un bambino di 2 anni in pieno benessere giunge al Pronto Soccorso per il reperto di massa addominale destra palpabile non dolente. Dopo iniziali accertamenti viene ipotizzata la diagnosi di tumore di Wilms. Quale delle seguenti affermazioni riguardante questa neoplasia infantile è ERRATA?</t>
+  </si>
+  <si>
     <t>Un neonato di tre settimane di vita giunge in Pronto Soccorso per vomito alimentare ingravescente. A seguito di accertamenti viene posta diagnosi di stenosi ipertrofica del piloro. Quale delle seguenti affermazioni NON è corretta?</t>
   </si>
   <si>
+    <t>Un bambino di 10 anni riferisce l’insorgenza di dolore dopo un trauma alla spalla destra riportato durante una partita di calcio. I genitori negano precedenti dolori o traumi alla stessa spalla. La radiografia è mostrata nella figura. Qual è la diagnosi più probabile fra le seguenti?</t>
+  </si>
+  <si>
+    <t>Una donna di 54 anni giunge al Pronto Soccorso per violenta cefalea nucale a esordio improvviso, durante uno sforzo fisico. La paziente si presenta sveglia, collaborante e apiretica, con lieve emiparesi destra e con rigidità nucale. Il sospetto clinico è di emorragia sub- aracnoidea. Quale tra questi è l’accertamento strumentale indicato in prima istanza per questa situazione?</t>
+  </si>
+  <si>
+    <t>Riguardo la chiusura percutanea del forame ovale pervio (PFO) in un paziente di 60 anni, quale delle seguenti affermazioni è corretta?</t>
+  </si>
+  <si>
+    <t>Una paziente di 31 anni, originaria del Perù, presenta dolore e debolezza dell’arto superiore sinistro soprattutto al movimento di iperabduzione (test di Wright positivo), con anche comparsa di parestesie a livello della mano e del polso radiale, omolateralmente. In anamnesi, costa cervicale sovrannumeraria sinistra. Sulla base delle informazioni cliniche a disposizione quale delle seguenti appare la diagnosi più probabile?</t>
+  </si>
+  <si>
     <t>Un paziente si presenta dal medico con un piede pallido, dolente, con parestesie e scarsa motilità da qualche ora. Qual’è la diagnosi più probabile?</t>
   </si>
   <si>
+    <t>Un giovane si presenta con multipli polipi amartomatosi dell’intestino, iperpigmentazione muco-cutanea, specialmente della mucosa orale. La diagnosi più probabile è</t>
+  </si>
+  <si>
     <t>Quale gene è più frequentemente mutato nel melanoma cutaneo?</t>
   </si>
   <si>
+    <t>Paziente di 50 anni accede al Pronto Soccorso in regime di massima urgenza per trauma maggiore in seguito ad incidente stradale. Il paziente presenta stabilità emodinamica. La valutazione "ecografica fast" dimostra esile falda di versamento endoperitoneale maggiormente evidente in sede perisplenica. Il medico pone il sospetto di lesione traumatica della milza. In quale fase contrastografica TC può essere meglio visualizzata una lacerazione splenica</t>
+  </si>
+  <si>
+    <t>Qualora un uomo risultasse positivo al test genetico per la ricerca di mutazioni del gene BRCA2, in quale tra i seguenti organi avrebbe un rischio sensibilmente aumentato di sviluppare una neoplasia?</t>
+  </si>
+  <si>
+    <t>Tra i seguenti beta-bloccanti qual è selettivo per i recettori beta1?</t>
+  </si>
+  <si>
     <t>A seguito di caduta da un’impalcatura posta nel cantiere in cui stava lavorando, giunge in Pronto Soccorso un uomo di 40 anni, con politraumi e prognosi superiore ai 40 giorni. Il medico, trattandosi di lesioni verosimilmente colpose, deve</t>
   </si>
   <si>
     <t>Giunge all’osservazione un paziente di 49 anni con emangioblastoma cerebellare. In anamnesi, il paziente ha storia di feocromocitoma, cisti pancreatica e carcinoma a cellule renali. Quale tra le seguenti è la diagnosi più probabile?</t>
   </si>
   <si>
+    <t>Un uomo di 57 anni accusa diplopia orizzontale binoculare. La visione doppia peggiora nello sguardo verso destra. Quale tra le seguenti è la diagnosi più probabile</t>
+  </si>
+  <si>
+    <t>Un paziente di otto anni viene accompagnato al Pronto Soccorso per comparsa di tumefazione cervicale mediana anteriore, dolorabile ed iperemica. Agli atti deglutitori si apprezza rapporto con l’osso ioide. Quale tra le seguenti è la diagnosi più probabile?</t>
+  </si>
+  <si>
+    <t>Un uomo di 55 anni affetto da molto tempo da disturbi dispeptici viene alla osservazione per una tumefazione della fossa clavicolare sinistra (Segno di Troisier). Qual è il sospetto diagnostico più verosimile tra i seguenti?</t>
+  </si>
+  <si>
     <t>Un uomo di 62 anni ha di recente sviluppato un diabete mellito con costante perdita di peso e dolore puntorio localizzato ai quadranti superiori dell'addome ed irradiato al dorso. Qual è il sospetto diagnostico più probabile tra i seguenti?</t>
   </si>
   <si>
     <t>Paziente giunge in Pronto Soccorso con dolore addominale associato a febbre con brivido ed ittero. Come si chiama l’associazione dei tre segni clinici presentati dal paziente?</t>
   </si>
   <si>
+    <t>In un neonato, l’atresia esofagea di III tipo è</t>
+  </si>
+  <si>
+    <t>Una gestante di 45 anni alla diciassettesima settimana di gravidanza, con bitest risultato ad alto rischio per un’elevata translucenza nucale, si sottopone ad amniocentesi. Il risultato del cariotipo fetale evidenzia una trisomia del cromosoma 13 che determina la seguente sindrome</t>
+  </si>
+  <si>
+    <t>Viene portata dal pediatra una bambina di quattro anni che lamenta da alcuni giorni artralgie migranti e mialgie. L’esame obiettivo è sostanzialmente negativo. La madre riferisce che una settimana prima dell’esordio della sintomatologia aveva notato nella bambina la presenza di un’area eritematosa, con zona centrale più pallida sulla superficie posteriore della gamba sinistra, a livello del cavo popliteo, durata parecchi giorni e risoltasi spontaneamente. La bambina era stata in vacanza in una zona collinare del Friuli-Venezia Giulia. Quale tra le seguenti ipotesi diagnostiche è la più probabile?</t>
+  </si>
+  <si>
     <t>Giunge al reparto di dermatologia una paziente di 60 anni con eruzione maculo-papulosa morbilliforme diffusa, edema del volto, intenso prurito e febbre elevata. Tre settimane prima aveva iniziato un trattamento con allopurinolo. Si eseguono esami ematici con riscontro di ipereosinofilia (2000/mm3), linfociti atipici (più del 5%), aumento di transaminasi, lipasi e amilasi. Il quadro clinico è compatibile con</t>
   </si>
   <si>
@@ -331,12 +742,27 @@
     <t>Una donna di 59 anni, nepalese, non fumatrice, giunta in Italia da circa un mese, si presenta dal medico con tosse, febbricola serotina ed un recente episodio di emottisi. Riferisce calo ponderale di 2 Kg negli ultimi 2 mesi, nessuna comorbidità. Quale tra le seguenti è la diagnosi più probabile?</t>
   </si>
   <si>
+    <t>A seguito della comparsa di ittero, una paziente di 61 anni in buone condizioni cliniche generali esegue degli accertamenti diagnostici che si concludono con una diagnosi di tumore della testa del pancreas. La paziente viene sottoposta ad intervento chirurgico di duodenocefalopancreasectomia e l’esame istologico depone per “adenocarcinoma della testa del pancreas”. La stadiazione è pT2pN1M0. Quale trattamento medico è più indicato?</t>
+  </si>
+  <si>
     <t>Paziente HBsAg positivo con recente riscontro di massa palpabile in addome, esegue TC con MdC e.v. che evidenzia una lesione epatica sospetta per una diagnosi di epatocarcinoma. Qual è il comportamento contrastografico tipico dell’epatocarcinoma?</t>
   </si>
   <si>
     <t>Donna di 22 anni, accede al Pronto Soccorso per incidente stradale. Riferisce dolore addominale diffuso. PA: 130/70 mmHg, SpO2 97% in aria ambiente. ECO-FAST dubbia. Qual è l’indagine più appropriata per l’inquadramento diagnostico terapeutico tra le seguenti?</t>
   </si>
   <si>
+    <t>Paziente di 87 anni con dolore in regione dorsale. Quali reperti di rilievo si possono evidenziare in queste immagini RX e TC?</t>
+  </si>
+  <si>
+    <t>Donna, 23 anni, da circa due mesi presenta nodulo del quadrante superiore interno della mammella sinistra che, riferisce, è in accrescimento. Quando l’assistita si presenta al curante il nodulo è di 2,2 cm, clinicamente a margini netti, mobile, di consistenza teso- elastica. Viene eseguita biopsia eco-guidata il cui esame istologico mostra: “Lesione fibroepiteliale a cellularità stromale diffusamente aumentata in assenza di atipie; proliferazione ghiandolare con note di iperplasia duttale senza atipie. È presente 1 mitosi/10 HPF”. In base al quadro clinico e a quello istologico, quale è la diagnosi più probabile tra le seguenti?</t>
+  </si>
+  <si>
+    <t>Un uomo di 22 anni giunge in Pronto Soccorso, presenta febbre oltre i 38,5°C, rigidità nucale e forte cefalea. Viene eseguita una rachicentesi e alla lettura microscopica del vetrino, nel liquor cefalo-rachidiano si evidenziano numerosi polimorfonucleati e diplococchi Gram negativi. Quale tra i seguenti microrganismi è il probabile responsabile dell’infezione?</t>
+  </si>
+  <si>
+    <t>La diagnosi di fenilchetonuria avviene solitamente nell’ambito di</t>
+  </si>
+  <si>
     <t>Indicare, quale delle seguenti affermazioni concernenti ll Servizio Sanitario Nazionale è corretta</t>
   </si>
   <si>
@@ -349,33 +775,114 @@
     <t>Una donna di 65 anni affetta da gonalgia sinistra, di origine artrosica e trattata recentemente con iniezioni intra-articolari di acido ialuronico, si rivolge al pronto soccorso per improvvisa tumefazione del ginocchio sinistro, insorgenza di febbre (TC 38.2°C) e malessere generale. Agli esami di laboratorio si evidenzia un marcato rialzo degli indici di flogosi e leucocitosi neutrofila. Quale tra i seguenti esami andrà tempestivamente eseguito?</t>
   </si>
   <si>
+    <t>Una donna di 78 anni, trattata all’età di 58 anni con mastectomia totale e radioterapia per un carcinoma della mammella, nelle ultime settimane ha notato la presenza di numerose lesioni bluastre a livello della cicatrice del pregresso intervento. A tale livello viene effettuata biopsia incisionale che all’esame istologico mostra: “numerosi vasi con pareti ispessite, variamente anastomizzati fra loro, rivestiti da cellule rigonfie e con numerose figure mitotiche”. In base al quadro clinico ed al reperto istologico, quale tra le seguenti è la diagnosi più probabile?</t>
+  </si>
+  <si>
+    <t>Un paziente forte fumatore di 68 anni sviluppa acutamente dolore all’arto inferiore destro con deficit sensitivo-motorio in prima giornata postoperatoria dopo intervento di stabilizzazione mediante vite-placca per frattura di femore destro. L’arto interessato appare freddo e pallido; il polso popliteo è iposfigmico, il polso pedidio è assente. Quale dei seguenti accertamenti è indicato in prima istanza?</t>
+  </si>
+  <si>
+    <t>Un signore di 56 anni viene ricoverato in Terapia Intensiva in seguito a crisi comiziale con perdita di coscienza. In anamnesi patologica remota: resezione di meningioma temporale destro in follow up (ultimo controllo 3 mesi prima), terapia con litio per sindrome bipolare insorta dopo chirurgia. In quinta giornata di degenza il paziente è vigile, orientato, non ha deficit di sensibilità-motilità degli arti, GCS 15 ma riferisce polidipsia, con poliuria (diuresi 2,5 ml/Kg/h) con urine limpide, osmolarità urinaria &lt;150 mOsm/L, sodiemia 153 mEq/L e potassiemia 3 mEq/L Litiemia 1,4 mmol/L (vn 0,4-0,8 mmol/L) Quale tra le seguenti è l’ipotesi più probabile?</t>
+  </si>
+  <si>
     <t>Maschio di 66 anni presenta una anemia severa (Hb 4,9 g/dL), microcitica (MCV 64,4 fL) e ipocromica (MCH 19,9 pg). L’assetto marziale evidenzia una sideremia di 17 µg/dL (valori di riferimento: 37 - 145 µg/dL) e una ferritinemia di 2 ng/mL (valori di riferimento: 15 - 200 ng/mL). Quale delle seguenti condizioni va considerata per prima?</t>
   </si>
   <si>
+    <t>Un paziente di 89 anni presenta una estesa lesione parzialmente ulcerata della cute del naso non trattabile chirurgicamente. Quale delle seguenti diagnosi istologiche costituisce un’indicazione alla radioterapia?</t>
+  </si>
+  <si>
     <t>Un uomo di 75 anni affetto da cirrosi epatica HCV relata, esegue una TC addome con riscontro di nodulo epatico di 22 mm di diametro con il seguente comportamento contrasto-grafico: wash-in in fase arteriosa e wash-out in fase venosa. Qual è la diagnosi più probabile?</t>
   </si>
   <si>
     <t>Una paziente di 40 anni, portatrice di mutazione del gene BRCA1, attualmente sana, è in lista per intervento di mastectomia profilattica bilaterale (risk reducing). Quale strategia è la più appropriata fra le seguenti?</t>
   </si>
   <si>
+    <t>Quale delle seguenti è una controindicazione assoluta al trapianto di fegato per metastasi epatiche da adenocarcinoma del colon retto?</t>
+  </si>
+  <si>
     <t>Una paziente di 34 anni, con diagnosi di morbo di Crohn da 10 anni, si presenta in ambulatorio con dolore addominale cronico localizzato in fossa iliaca destra, diarrea intermittente e perdita di peso di circa 8 kg negli ultimi sei mesi. Poichè non risponde più adeguatamente alla terapia medica, si decide di procedere chirurgicamente. Tutte le seguenti procedure possono trovare indicazione nella terapia chirurgica del morbo di Crohn, TRANNE</t>
   </si>
   <si>
+    <t>Una giovane donna dopo un prolungato travaglio ed un parto complicato da una rottura prematura delle membrane amnio-coriali presenta, in seconda giornata, febbre con brivido associata ad ipotensione arteriosa sistemica e intenso dolore addominale. La diagnosi è: “sospetta endometrite puerperale”. Viene effettuato un RX torace che risulta essere nei limiti della norma. Improvvisamente la paziente presenta dispnea e SpO2 82% in aria ambiente che non aumenta anche con somministrazione di ossigenoterapia con FiO2 100%. Non emottisi. Si decide quindi di intubare e ventilare la paziente con FiO2 80% e l’emogasanalisi arteriosa di controllo evidenzia PaO2 di 62 mmHg e PaCO2 di 33 mmHg. Al controllo della RX torace è presente il quadro riportato. BNP, creatininemia ed emoglobina nei limiti della norma. Quale tra le seguenti diagnosi è la più probabile?</t>
+  </si>
+  <si>
+    <t>t(11;22)</t>
+  </si>
+  <si>
     <t>Asma allergico</t>
   </si>
   <si>
+    <t>PET-TC total body</t>
+  </si>
+  <si>
+    <t>Esplorazione digitale del retto e anoscopia</t>
+  </si>
+  <si>
+    <t>Ketoprofene</t>
+  </si>
+  <si>
     <t>Sindrome di Turner</t>
   </si>
   <si>
     <t>TVP in atto</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>TC con mezzo di contrasto</t>
+  </si>
+  <si>
+    <t>Rinite allergica</t>
+  </si>
+  <si>
+    <t>Lavaggi nasali con soluzione fisiologica, terapia antistaminica per os, spray cortisonico nasale</t>
+  </si>
+  <si>
+    <t>La velocità di crescità è ridotta</t>
+  </si>
+  <si>
+    <t>TC encefalo</t>
+  </si>
+  <si>
+    <t>L'urinocoltura da sacchetto è la metodica più affidabile per l'esame colturale delle urine</t>
+  </si>
+  <si>
+    <t>solo nelle forme complicate, con stato settico del paziente</t>
+  </si>
+  <si>
+    <t>Terapia con farmaci antipsicotici long-acting</t>
+  </si>
+  <si>
+    <t>Colchicina</t>
+  </si>
+  <si>
+    <t>Acido urico</t>
+  </si>
+  <si>
+    <t>adrenalina</t>
+  </si>
+  <si>
+    <t>Intralipid 20%</t>
+  </si>
+  <si>
+    <t>il farmaco di scelta nell'intossicazione acuta da oppiacei</t>
+  </si>
+  <si>
     <t>un'estroflessione della parete intestinale a fondo cieco a livello dell'ileo</t>
   </si>
   <si>
     <t>Ragade anale</t>
   </si>
   <si>
+    <t>Agonisti del recettore della 5-idrossitriptamina (5-HT1)</t>
+  </si>
+  <si>
+    <t>Cistite da E.coli</t>
+  </si>
+  <si>
+    <t>Anemia da carenza di vitamina B12 causata da dieta vegana</t>
+  </si>
+  <si>
     <t>la legge 833/1978</t>
   </si>
   <si>
@@ -394,6 +901,9 @@
     <t>Adenocarcinoma delle cavità nasali e paranasali</t>
   </si>
   <si>
+    <t>Ezetimibe</t>
+  </si>
+  <si>
     <t>Spironolattone</t>
   </si>
   <si>
@@ -403,9 +913,18 @@
     <t>Ecografia renale</t>
   </si>
   <si>
+    <t>Herpes simplex virus tipo 2</t>
+  </si>
+  <si>
+    <t>Herpes zoster oticus</t>
+  </si>
+  <si>
     <t>Cisti del dotto tireoglosso</t>
   </si>
   <si>
+    <t>Beta-bloccanti</t>
+  </si>
+  <si>
     <t>Stenosi ipertrofica del piloro</t>
   </si>
   <si>
@@ -421,12 +940,27 @@
     <t>Per la loro misurazione è necessaria una TC coronarica con mezzo di contrasto</t>
   </si>
   <si>
+    <t>Analoghi dei difosfonati</t>
+  </si>
+  <si>
+    <t>Cistinuria</t>
+  </si>
+  <si>
     <t>Metilprednisolone</t>
   </si>
   <si>
+    <t>Ipercalcemia</t>
+  </si>
+  <si>
     <t>Anemia falciforme</t>
   </si>
   <si>
+    <t>Sindrome di Treacher-Collins</t>
+  </si>
+  <si>
+    <t>Leydigoma</t>
+  </si>
+  <si>
     <t>Test delle feci per dosaggio dell'antigene e delle tossine del Clostridium difficile</t>
   </si>
   <si>
@@ -442,42 +976,135 @@
     <t>Embolia polmonare acuta da trombosi venosa profonda</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>9%</t>
+  </si>
+  <si>
+    <t>Sifiloma primario</t>
+  </si>
+  <si>
+    <t>Antagonista degli oppiacei</t>
+  </si>
+  <si>
     <t>Angio-TC nel sospetto di embolia polmonare acuta</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Tossicità sistemica da anestetici locali</t>
+  </si>
+  <si>
     <t>Ipovolemia (relativa o assoluta)</t>
   </si>
   <si>
+    <t>Ha previsto la costituzione delle Aziende Sanitarie Locali</t>
+  </si>
+  <si>
+    <t>Fumo di sigaretta</t>
+  </si>
+  <si>
+    <t>Nessun diritto ad indennizzo</t>
+  </si>
+  <si>
     <t>Magnesio</t>
   </si>
   <si>
+    <t>E’ un paziente fragile con un rischio di eventi clinici negativi aumentato</t>
+  </si>
+  <si>
     <t>Antracicline</t>
   </si>
   <si>
+    <t>Inibitori del cotrasportatore sodio-glucosio tipo 2 (SGLT2i)</t>
+  </si>
+  <si>
+    <t>TC torace senza mezzo di contrasto</t>
+  </si>
+  <si>
     <t>Scompenso cardiaco</t>
   </si>
   <si>
+    <t>Malattia ateroembolica</t>
+  </si>
+  <si>
+    <t>Leptospirosi ittero-emorragica</t>
+  </si>
+  <si>
+    <t>Prolattinoma ipofisario</t>
+  </si>
+  <si>
+    <t>Esketamina</t>
+  </si>
+  <si>
+    <t>Nella maggior parte dei casi la fistola esofago-tracheale è prossimale all’atresia esofagea</t>
+  </si>
+  <si>
+    <t>E’ un tumore tipicamente a crescita infiltrativa</t>
+  </si>
+  <si>
     <t>Ha prognosi infausta anche se trattata chirurgicamente</t>
   </si>
   <si>
+    <t>Cisti ossea giovanile</t>
+  </si>
+  <si>
+    <t>TC cerebrale + Angio-TC cerebrale</t>
+  </si>
+  <si>
+    <t>E’ una procedura che ha come principale indicazione la prevenzione dell’ictus cardioembolico</t>
+  </si>
+  <si>
+    <t>Sindrome dello stretto toracico superiore</t>
+  </si>
+  <si>
     <t>Ischemia acuta</t>
   </si>
   <si>
+    <t>Sindrome di Peutz-Jeghers</t>
+  </si>
+  <si>
     <t>BRAF</t>
   </si>
   <si>
+    <t>Fase bifasica arteriosa-venosa</t>
+  </si>
+  <si>
+    <t>Prostata</t>
+  </si>
+  <si>
+    <t>Atenololo</t>
+  </si>
+  <si>
     <t>Redigere denuncia di reato all’Autorità Giudiziaria</t>
   </si>
   <si>
     <t>Sindrome di Von Hippel-Lindau</t>
   </si>
   <si>
+    <t>Paralisi isolata del VI nervo cranico di destra</t>
+  </si>
+  <si>
+    <t>Tumore dello stomaco</t>
+  </si>
+  <si>
     <t>Tumore del pancreas avanzato</t>
   </si>
   <si>
     <t>Triade di Charcot</t>
   </si>
   <si>
+    <t>La forma più frequente</t>
+  </si>
+  <si>
+    <t>Patau</t>
+  </si>
+  <si>
+    <t>Malattia di Lyme</t>
+  </si>
+  <si>
     <t>Drug Rash with Eosinophilia and Systemic Symptoms (DRESS)</t>
   </si>
   <si>
@@ -487,12 +1114,27 @@
     <t>Tubercolosi polmonare</t>
   </si>
   <si>
+    <t>Chemioterapico adiuvante secondo lo schema FOLFIRINOX</t>
+  </si>
+  <si>
     <t>Wash-in arterioso con wash-out portale-tardivo</t>
   </si>
   <si>
     <t>TC spirale dell’addome con MdC</t>
   </si>
   <si>
+    <t>Crollo vertebrale dorsale</t>
+  </si>
+  <si>
+    <t>Fibroadenoma</t>
+  </si>
+  <si>
+    <t>Neisseria meningitidis</t>
+  </si>
+  <si>
+    <t>Un programma di screening neonatale basato sulla determinazione dei livelli plasmatici di fenilalanina misurati almeno 48 ore dopo la nascita</t>
+  </si>
+  <si>
     <t>I Livelli Essenziali di Assistenza (LEA) sono costituiti dall’insieme delle attività, dei servizi e delle prestazioni che il Servizio Sanitario Nazionale eroga a tutti i cittadini gratuitamente o con il pagamento di un ticket, indipendentemente dal reddito e dal luogo di residenza</t>
   </si>
   <si>
@@ -505,28 +1147,97 @@
     <t>Esame citochimico e colturale del liquido sinoviale</t>
   </si>
   <si>
+    <t>Angiosarcoma</t>
+  </si>
+  <si>
+    <t>Ecodoppler AAII (arti inferiori)</t>
+  </si>
+  <si>
+    <t>Diabete insipido nefrogenico</t>
+  </si>
+  <si>
     <t>Emorragia cronica di origine gastroenterica</t>
   </si>
   <si>
+    <t>Carcinoma spinocellulare</t>
+  </si>
+  <si>
     <t>Epatocarcinoma</t>
   </si>
   <si>
     <t>Nessuna procedura sul cavo ascellare</t>
   </si>
   <si>
+    <t>Carcinosi peritoneale</t>
+  </si>
+  <si>
     <t>miotomia extramucosa di Heller</t>
   </si>
   <si>
+    <t>Sindrome da distress respiratorio acuto (ARDS)</t>
+  </si>
+  <si>
+    <t>Oncologia; Genetica Medica</t>
+  </si>
+  <si>
     <t>Pneumologia e Chirurgia Toracica</t>
   </si>
   <si>
+    <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+  </si>
+  <si>
+    <t>Chirurgia Generale; Gastroenterologia</t>
+  </si>
+  <si>
+    <t>Farmacologia e Tossicologia; Gastroenterologia</t>
+  </si>
+  <si>
     <t>Ginecologia e Ostetricia; Genetica Medica</t>
   </si>
   <si>
     <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
   </si>
   <si>
-    <t>Chirurgia Generale; Gastroenterologia</t>
+    <t>Neurologia e Neurochirurgia; Anestesia e Rianimazione</t>
+  </si>
+  <si>
+    <t>Otorinolaringoiatria; Immunologia e Reumatologia</t>
+  </si>
+  <si>
+    <t>Endocrinologia; Pediatria</t>
+  </si>
+  <si>
+    <t>Pediatria; Diagnostica per Immagini e Medicina Nucleare</t>
+  </si>
+  <si>
+    <t>Pediatria; Urologia</t>
+  </si>
+  <si>
+    <t>Psichiatria; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
+    <t>Immunologia e Reumatologia; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
+    <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
+  </si>
+  <si>
+    <t>Anestesia e Rianimazione</t>
+  </si>
+  <si>
+    <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
+    <t>Farmacologia e Tossicologia; Anestesia e Rianimazione</t>
+  </si>
+  <si>
+    <t>Neurologia e Neurochirurgia; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
+    <t>Malattie Infettive</t>
+  </si>
+  <si>
+    <t>Ematologia; Ginecologia e Ostetricia</t>
   </si>
   <si>
     <t>Medicina Legale</t>
@@ -535,9 +1246,6 @@
     <t>Diagnostica per Immagini e Medicina Nucleare; Pneumologia e Chirurgia Toracica</t>
   </si>
   <si>
-    <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
-  </si>
-  <si>
     <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
@@ -547,18 +1255,27 @@
     <t>Medicina del Lavoro; Oncologia</t>
   </si>
   <si>
+    <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+  </si>
+  <si>
     <t>Nefrologia; Farmacologia e Tossicologia</t>
   </si>
   <si>
     <t>Nefrologia; Endocrinologia</t>
   </si>
   <si>
-    <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
+    <t>Malattie Infettive; Ginecologia e Ostetricia</t>
+  </si>
+  <si>
+    <t>Otorinolaringoiatria; Neurologia e Neurochirurgia</t>
   </si>
   <si>
     <t>Chirurgia Generale; Pediatria</t>
   </si>
   <si>
+    <t>Neurologia e Neurochirurgia; Pediatria</t>
+  </si>
+  <si>
     <t>Pediatria; Chirurgia Generale</t>
   </si>
   <si>
@@ -574,12 +1291,24 @@
     <t>Diagnostica per Immagini e Medicina Nucleare; Cardiologia e Cardiochirurgia</t>
   </si>
   <si>
+    <t>Nefrologia; Urologia</t>
+  </si>
+  <si>
     <t>Endocrinologia; Farmacologia e Tossicologia</t>
   </si>
   <si>
+    <t>Pediatria; Oncologia</t>
+  </si>
+  <si>
     <t>Ematologia; Pediatria</t>
   </si>
   <si>
+    <t>Genetica Medica; Otorinolaringoiatria</t>
+  </si>
+  <si>
+    <t>Urologia; Oncologia</t>
+  </si>
+  <si>
     <t>Malattie Infettive; Gastroenterologia</t>
   </si>
   <si>
@@ -592,27 +1321,87 @@
     <t>Genetica Medica; Oncologia</t>
   </si>
   <si>
+    <t>Malattie Infettive; Pediatria</t>
+  </si>
+  <si>
+    <t>Chirurgia Generale</t>
+  </si>
+  <si>
+    <t>Dermatologia e Venereologia; Ginecologia e Ostetricia</t>
+  </si>
+  <si>
     <t>Anestesia e Rianimazione; Pneumologia e Chirurgia Toracica</t>
   </si>
   <si>
+    <t>Anestesia e Rianimazione; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
     <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
   </si>
   <si>
+    <t>Medicina Legale; Igiene, Epidemiologia e Statistica</t>
+  </si>
+  <si>
+    <t>Pneumologia e Chirurgia Toracica; Medicina del Lavoro</t>
+  </si>
+  <si>
+    <t>Medicina Legale; Medicina del Lavoro</t>
+  </si>
+  <si>
+    <t>Medicina Interna; Nutrizione Clinica</t>
+  </si>
+  <si>
     <t>Oncologia; Cardiologia e Cardiochirurgia</t>
   </si>
   <si>
-    <t>Chirurgia Generale</t>
+    <t>Cardiologia e Cardiochirurgia; Endocrinologia</t>
+  </si>
+  <si>
+    <t>Nefrologia; Cardiologia e Cardiochirurgia</t>
+  </si>
+  <si>
+    <t>Malattie Infettive; Nefrologia</t>
+  </si>
+  <si>
+    <t>Endocrinologia; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Ortopedia e Traumatologia; Pediatria</t>
+  </si>
+  <si>
+    <t>Neurologia e Neurochirurgia; Diagnostica per Immagini e Medicina Nucleare</t>
+  </si>
+  <si>
+    <t>Cardiologia e Cardiochirurgia</t>
+  </si>
+  <si>
+    <t>Ortopedia e Traumatologia; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Gastroenterologia; Genetica Medica</t>
   </si>
   <si>
     <t>Oncologia; Dermatologia e Venereologia</t>
   </si>
   <si>
+    <t>Diagnostica per Immagini e Medicina Nucleare; Chirurgia Generale</t>
+  </si>
+  <si>
+    <t>Oftalmologia; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Otorinolaringoiatria; Pediatria</t>
+  </si>
+  <si>
     <t>Oncologia; Gastroenterologia</t>
   </si>
   <si>
     <t>Gastroenterologia; Chirurgia Generale</t>
   </si>
   <si>
+    <t>Pediatria; Malattie Infettive</t>
+  </si>
+  <si>
     <t>Dermatologia e Venereologia; Farmacologia e Tossicologia</t>
   </si>
   <si>
@@ -622,9 +1411,24 @@
     <t>Pneumologia e Chirurgia Toracica; Malattie Infettive</t>
   </si>
   <si>
+    <t>Oncologia; Chirurgia Generale</t>
+  </si>
+  <si>
     <t>Chirurgia Generale; Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
+    <t>Diagnostica per Immagini e Medicina Nucleare; Ortopedia e Traumatologia</t>
+  </si>
+  <si>
+    <t>Ginecologia e Ostetricia; Oncologia</t>
+  </si>
+  <si>
+    <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Genetica Medica; Pediatria</t>
+  </si>
+  <si>
     <t>Medicina del Lavoro; Otorinolaringoiatria</t>
   </si>
   <si>
@@ -634,37 +1438,91 @@
     <t>Immunologia e Reumatologia; Ortopedia e Traumatologia</t>
   </si>
   <si>
+    <t>Chirurgia Generale; Ortopedia e Traumatologia</t>
+  </si>
+  <si>
     <t>Ematologia; Gastroenterologia</t>
   </si>
   <si>
+    <t>Dermatologia e Venereologia; Oncologia</t>
+  </si>
+  <si>
     <t>Chirurgia Generale; Oncologia</t>
   </si>
   <si>
+    <t>Anestesia e Rianimazione; Ginecologia e Ostetricia</t>
+  </si>
+  <si>
+    <t>Oncologia</t>
+  </si>
+  <si>
     <t>Pneumologia e Chirurgia Toracica; Pediatria</t>
   </si>
   <si>
+    <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
+  </si>
+  <si>
+    <t>Gastroenterologia; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
     <t>Genetica Medica; Ginecologia e Ostetricia</t>
   </si>
   <si>
+    <t>Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
+  </si>
+  <si>
+    <t>Otorinolaringoiatria</t>
+  </si>
+  <si>
+    <t>Pediatria; Endocrinologia</t>
+  </si>
+  <si>
+    <t>Pediatria; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Pediatria; Nefrologia</t>
+  </si>
+  <si>
+    <t>Psichiatria</t>
+  </si>
+  <si>
+    <t>Immunologia e Reumatologia</t>
+  </si>
+  <si>
+    <t>Urologia</t>
+  </si>
+  <si>
+    <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
+  </si>
+  <si>
+    <t>Farmacologia e Tossicologia</t>
+  </si>
+  <si>
+    <t>Dermatologia e Venereologia; Malattie Infettive</t>
+  </si>
+  <si>
+    <t>Ginecologia e Ostetricia; Ematologia</t>
+  </si>
+  <si>
     <t>Igiene, Epidemiologia e Statistica</t>
   </si>
   <si>
     <t>Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
-    <t>Farmacologia e Tossicologia</t>
-  </si>
-  <si>
     <t>Medicina del Lavoro</t>
   </si>
   <si>
+    <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+  </si>
+  <si>
     <t>Endocrinologia</t>
   </si>
   <si>
-    <t>Urologia</t>
-  </si>
-  <si>
-    <t>Otorinolaringoiatria</t>
+    <t>Dermatologia e Venereologia</t>
   </si>
   <si>
     <t>Pediatria</t>
@@ -679,36 +1537,45 @@
     <t>Ematologia</t>
   </si>
   <si>
-    <t>Malattie Infettive</t>
+    <t>Genetica Medica</t>
   </si>
   <si>
     <t>Genetica Medica; Gastroenterologia</t>
   </si>
   <si>
-    <t>Anestesia e Rianimazione</t>
+    <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
+  </si>
+  <si>
+    <t>Anestesia e Rianimazione; Chirurgia Generale</t>
+  </si>
+  <si>
+    <t>Medicina del Lavoro; Medicina Legale</t>
+  </si>
+  <si>
+    <t>Medicina Interna</t>
   </si>
   <si>
     <t>Cardiologia e Cardiochirurgia; Oncologia</t>
   </si>
   <si>
-    <t>Cardiologia e Cardiochirurgia</t>
-  </si>
-  <si>
-    <t>Dermatologia e Venereologia; Oncologia</t>
-  </si>
-  <si>
-    <t>Medicina Legale; Medicina del Lavoro</t>
-  </si>
-  <si>
-    <t>Genetica Medica</t>
+    <t>Endocrinologia; Cardiologia e Cardiochirurgia</t>
+  </si>
+  <si>
+    <t>Oncologia; Pediatria</t>
+  </si>
+  <si>
+    <t>Ortopedia e Traumatologia</t>
+  </si>
+  <si>
+    <t>Cardiologia e Cardiochirurgia; Neurologia e Neurochirurgia</t>
+  </si>
+  <si>
+    <t>Oftalmologia</t>
   </si>
   <si>
     <t>Gastroenterologia; Oncologia</t>
   </si>
   <si>
-    <t>Dermatologia e Venereologia</t>
-  </si>
-  <si>
     <t>Malattie Infettive; Otorinolaringoiatria</t>
   </si>
   <si>
@@ -718,7 +1585,7 @@
     <t>Diagnostica per Immagini e Medicina Nucleare; Gastroenterologia</t>
   </si>
   <si>
-    <t>Diagnostica per Immagini e Medicina Nucleare; Chirurgia Generale</t>
+    <t>Ortopedia e Traumatologia; Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
     <t>Anestesia e Rianimazione; Malattie Infettive</t>
@@ -730,9 +1597,6 @@
     <t>Gastroenterologia; Ematologia</t>
   </si>
   <si>
-    <t>Oncologia; Chirurgia Generale</t>
-  </si>
-  <si>
     <t>Medicina Interna; Pneumologia e Chirurgia Toracica</t>
   </si>
   <si>
@@ -742,7 +1606,7 @@
     <t>Cardiologia e Cardiochirurgia; Medicina Interna</t>
   </si>
   <si>
-    <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+    <t>Oncologia; Neurologia e Neurochirurgia</t>
   </si>
   <si>
     <t>Otorinolaringoiatria; Oncologia</t>
@@ -751,15 +1615,12 @@
     <t>Nefrologia; Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
-    <t>Otorinolaringoiatria; Pediatria</t>
+    <t>Neurologia e Neurochirurgia; Otorinolaringoiatria</t>
   </si>
   <si>
     <t>Gastroenterologia; Pediatria</t>
   </si>
   <si>
-    <t>Oncologia</t>
-  </si>
-  <si>
     <t>Farmacologia e Tossicologia; Medicina Interna</t>
   </si>
   <si>
@@ -769,46 +1630,58 @@
     <t>Gastroenterologia; Malattie Infettive</t>
   </si>
   <si>
+    <t>Chirurgia Generale; Dermatologia e Venereologia</t>
+  </si>
+  <si>
     <t>Ortopedia e Traumatologia; Cardiologia e Cardiochirurgia</t>
   </si>
   <si>
-    <t>Medicina Interna</t>
-  </si>
-  <si>
     <t>Neurologia e Neurochirurgia; Genetica Medica</t>
   </si>
   <si>
-    <t>Immunologia e Reumatologia</t>
+    <t>Ginecologia e Ostetricia</t>
   </si>
   <si>
     <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
   </si>
   <si>
+    <t>Malattie Infettive; Dermatologia e Venereologia</t>
+  </si>
+  <si>
     <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
   </si>
   <si>
     <t>Pneumologia e Chirurgia Toracica; Anestesia e Rianimazione</t>
   </si>
   <si>
+    <t>Medicina del Lavoro; Pneumologia e Chirurgia Toracica</t>
+  </si>
+  <si>
     <t>Oncologia; Farmacologia e Tossicologia</t>
   </si>
   <si>
-    <t>Oncologia; Genetica Medica</t>
+    <t>Cardiologia e Cardiochirurgia; Nefrologia</t>
+  </si>
+  <si>
+    <t>Neurologia e Neurochirurgia; Endocrinologia</t>
+  </si>
+  <si>
+    <t>Ortopedia e Traumatologia; Pneumologia e Chirurgia Toracica</t>
+  </si>
+  <si>
+    <t>Neurologia e Neurochirurgia; Oftalmologia</t>
   </si>
   <si>
     <t>Farmacologia e Tossicologia; Dermatologia e Venereologia</t>
   </si>
   <si>
+    <t>Ginecologia e Ostetricia; Chirurgia Generale</t>
+  </si>
+  <si>
     <t>Anestesia e Rianimazione; Urologia</t>
   </si>
   <si>
-    <t>Ortopedia e Traumatologia</t>
-  </si>
-  <si>
-    <t>Neurologia e Neurochirurgia</t>
-  </si>
-  <si>
-    <t>Ginecologia e Ostetricia</t>
+    <t>Ortopedia e Traumatologia; Chirurgia Generale</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1209,34 +2082,34 @@
         <v>2017</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="G2" t="s">
-        <v>208</v>
+        <v>479</v>
       </c>
       <c r="H2" t="s">
-        <v>239</v>
+        <v>387</v>
       </c>
       <c r="I2" t="s">
-        <v>167</v>
+        <v>479</v>
       </c>
       <c r="J2" t="s">
-        <v>252</v>
+        <v>479</v>
       </c>
       <c r="K2" t="s">
-        <v>167</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1244,34 +2117,34 @@
         <v>2017</v>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>480</v>
       </c>
       <c r="H3" t="s">
-        <v>240</v>
+        <v>527</v>
       </c>
       <c r="I3" t="s">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="J3" t="s">
-        <v>214</v>
+        <v>512</v>
       </c>
       <c r="K3" t="s">
-        <v>264</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1279,559 +2152,559 @@
         <v>2017</v>
       </c>
       <c r="B4">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>169</v>
+        <v>389</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>481</v>
       </c>
       <c r="H4" t="s">
-        <v>241</v>
+        <v>410</v>
       </c>
       <c r="I4" t="s">
-        <v>167</v>
+        <v>481</v>
       </c>
       <c r="J4" t="s">
-        <v>225</v>
+        <v>388</v>
       </c>
       <c r="K4" t="s">
-        <v>167</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="H5" t="s">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="I5" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="J5" t="s">
-        <v>218</v>
+        <v>436</v>
       </c>
       <c r="K5" t="s">
-        <v>195</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>391</v>
       </c>
       <c r="G6" t="s">
-        <v>195</v>
+        <v>482</v>
       </c>
       <c r="H6" t="s">
-        <v>218</v>
+        <v>391</v>
       </c>
       <c r="I6" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
       <c r="J6" t="s">
-        <v>218</v>
+        <v>494</v>
       </c>
       <c r="K6" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B7">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="F7" t="s">
-        <v>171</v>
+        <v>392</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>483</v>
       </c>
       <c r="H7" t="s">
-        <v>213</v>
+        <v>528</v>
       </c>
       <c r="I7" t="s">
-        <v>256</v>
+        <v>392</v>
       </c>
       <c r="J7" t="s">
-        <v>213</v>
+        <v>501</v>
       </c>
       <c r="K7" t="s">
-        <v>210</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>172</v>
+        <v>393</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>388</v>
       </c>
       <c r="H8" t="s">
-        <v>202</v>
+        <v>529</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>388</v>
       </c>
       <c r="J8" t="s">
-        <v>195</v>
+        <v>452</v>
       </c>
       <c r="K8" t="s">
-        <v>211</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>394</v>
       </c>
       <c r="G9" t="s">
-        <v>212</v>
+        <v>484</v>
       </c>
       <c r="H9" t="s">
-        <v>212</v>
+        <v>484</v>
       </c>
       <c r="I9" t="s">
-        <v>223</v>
+        <v>394</v>
       </c>
       <c r="J9" t="s">
-        <v>212</v>
+        <v>484</v>
       </c>
       <c r="K9" t="s">
-        <v>223</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B10">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>389</v>
       </c>
       <c r="G10" t="s">
-        <v>167</v>
+        <v>485</v>
       </c>
       <c r="H10" t="s">
-        <v>219</v>
+        <v>530</v>
       </c>
       <c r="I10" t="s">
-        <v>167</v>
+        <v>479</v>
       </c>
       <c r="J10" t="s">
-        <v>225</v>
+        <v>479</v>
       </c>
       <c r="K10" t="s">
-        <v>167</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B11">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>272</v>
       </c>
       <c r="F11" t="s">
-        <v>175</v>
+        <v>395</v>
       </c>
       <c r="G11" t="s">
-        <v>167</v>
+        <v>486</v>
       </c>
       <c r="H11" t="s">
-        <v>242</v>
+        <v>486</v>
       </c>
       <c r="I11" t="s">
-        <v>167</v>
+        <v>395</v>
       </c>
       <c r="J11" t="s">
-        <v>225</v>
+        <v>486</v>
       </c>
       <c r="K11" t="s">
-        <v>167</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>273</v>
       </c>
       <c r="F12" t="s">
-        <v>176</v>
+        <v>395</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>486</v>
       </c>
       <c r="H12" t="s">
-        <v>243</v>
+        <v>486</v>
       </c>
       <c r="I12" t="s">
-        <v>213</v>
+        <v>395</v>
       </c>
       <c r="J12" t="s">
-        <v>216</v>
+        <v>486</v>
       </c>
       <c r="K12" t="s">
-        <v>213</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B13">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>274</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>396</v>
       </c>
       <c r="G13" t="s">
-        <v>212</v>
+        <v>487</v>
       </c>
       <c r="H13" t="s">
-        <v>242</v>
+        <v>487</v>
       </c>
       <c r="I13" t="s">
-        <v>212</v>
+        <v>503</v>
       </c>
       <c r="J13" t="s">
-        <v>225</v>
+        <v>503</v>
       </c>
       <c r="K13" t="s">
-        <v>212</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B14">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>275</v>
       </c>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>397</v>
       </c>
       <c r="G14" t="s">
-        <v>214</v>
+        <v>488</v>
       </c>
       <c r="H14" t="s">
-        <v>223</v>
+        <v>397</v>
       </c>
       <c r="I14" t="s">
-        <v>214</v>
+        <v>503</v>
       </c>
       <c r="J14" t="s">
-        <v>223</v>
+        <v>503</v>
       </c>
       <c r="K14" t="s">
-        <v>214</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B15">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>276</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>398</v>
       </c>
       <c r="G15" t="s">
-        <v>215</v>
+        <v>489</v>
       </c>
       <c r="H15" t="s">
-        <v>244</v>
+        <v>489</v>
       </c>
       <c r="I15" t="s">
-        <v>179</v>
+        <v>503</v>
       </c>
       <c r="J15" t="s">
-        <v>190</v>
+        <v>503</v>
       </c>
       <c r="K15" t="s">
-        <v>215</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B16">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="F16" t="s">
-        <v>180</v>
+        <v>398</v>
       </c>
       <c r="G16" t="s">
-        <v>216</v>
+        <v>461</v>
       </c>
       <c r="H16" t="s">
-        <v>245</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
-        <v>181</v>
+        <v>503</v>
       </c>
       <c r="J16" t="s">
-        <v>216</v>
+        <v>503</v>
       </c>
       <c r="K16" t="s">
-        <v>217</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B17">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>278</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>399</v>
       </c>
       <c r="G17" t="s">
-        <v>217</v>
+        <v>490</v>
       </c>
       <c r="H17" t="s">
-        <v>180</v>
+        <v>399</v>
       </c>
       <c r="I17" t="s">
-        <v>181</v>
+        <v>490</v>
       </c>
       <c r="J17" t="s">
-        <v>195</v>
+        <v>490</v>
       </c>
       <c r="K17" t="s">
-        <v>217</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B18">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
-        <v>182</v>
+        <v>400</v>
       </c>
       <c r="G18" t="s">
-        <v>218</v>
+        <v>491</v>
       </c>
       <c r="H18" t="s">
-        <v>246</v>
+        <v>473</v>
       </c>
       <c r="I18" t="s">
-        <v>182</v>
+        <v>491</v>
       </c>
       <c r="J18" t="s">
-        <v>218</v>
+        <v>491</v>
       </c>
       <c r="K18" t="s">
-        <v>217</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B19">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>401</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="H19" t="s">
-        <v>184</v>
+        <v>401</v>
       </c>
       <c r="I19" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="J19" t="s">
-        <v>211</v>
+        <v>492</v>
       </c>
       <c r="K19" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1839,34 +2712,34 @@
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="F20" t="s">
-        <v>184</v>
+        <v>402</v>
       </c>
       <c r="G20" t="s">
-        <v>211</v>
+        <v>493</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="I20" t="s">
-        <v>211</v>
+        <v>493</v>
       </c>
       <c r="J20" t="s">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="K20" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1874,1154 +2747,3744 @@
         <v>2018</v>
       </c>
       <c r="B21">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="F21" t="s">
-        <v>185</v>
+        <v>403</v>
       </c>
       <c r="G21" t="s">
-        <v>219</v>
+        <v>402</v>
       </c>
       <c r="H21" t="s">
-        <v>219</v>
+        <v>403</v>
       </c>
       <c r="I21" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
       <c r="J21" t="s">
-        <v>225</v>
+        <v>402</v>
       </c>
       <c r="K21" t="s">
-        <v>211</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="F22" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="G22" t="s">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="H22" t="s">
-        <v>248</v>
+        <v>404</v>
       </c>
       <c r="I22" t="s">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="J22" t="s">
-        <v>212</v>
+        <v>494</v>
       </c>
       <c r="K22" t="s">
-        <v>214</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B23">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="F23" t="s">
-        <v>187</v>
+        <v>390</v>
       </c>
       <c r="G23" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
       <c r="H23" t="s">
-        <v>249</v>
+        <v>504</v>
       </c>
       <c r="I23" t="s">
-        <v>187</v>
+        <v>436</v>
       </c>
       <c r="J23" t="s">
-        <v>217</v>
+        <v>504</v>
       </c>
       <c r="K23" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="F24" t="s">
-        <v>188</v>
+        <v>390</v>
       </c>
       <c r="G24" t="s">
-        <v>221</v>
+        <v>436</v>
       </c>
       <c r="H24" t="s">
-        <v>250</v>
+        <v>504</v>
       </c>
       <c r="I24" t="s">
-        <v>221</v>
+        <v>436</v>
       </c>
       <c r="J24" t="s">
-        <v>218</v>
+        <v>504</v>
       </c>
       <c r="K24" t="s">
-        <v>221</v>
+        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="E25" t="s">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="F25" t="s">
-        <v>189</v>
+        <v>405</v>
       </c>
       <c r="G25" t="s">
-        <v>214</v>
+        <v>484</v>
       </c>
       <c r="H25" t="s">
-        <v>189</v>
+        <v>405</v>
       </c>
       <c r="I25" t="s">
-        <v>178</v>
+        <v>484</v>
       </c>
       <c r="J25" t="s">
-        <v>214</v>
+        <v>484</v>
       </c>
       <c r="K25" t="s">
-        <v>190</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="F26" t="s">
-        <v>190</v>
+        <v>406</v>
       </c>
       <c r="G26" t="s">
-        <v>221</v>
+        <v>495</v>
       </c>
       <c r="H26" t="s">
-        <v>221</v>
+        <v>406</v>
       </c>
       <c r="I26" t="s">
-        <v>190</v>
+        <v>543</v>
       </c>
       <c r="J26" t="s">
-        <v>221</v>
+        <v>406</v>
       </c>
       <c r="K26" t="s">
-        <v>190</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B27">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
-        <v>191</v>
+        <v>407</v>
       </c>
       <c r="G27" t="s">
-        <v>222</v>
+        <v>496</v>
       </c>
       <c r="H27" t="s">
-        <v>229</v>
+        <v>407</v>
       </c>
       <c r="I27" t="s">
-        <v>247</v>
+        <v>506</v>
       </c>
       <c r="J27" t="s">
-        <v>218</v>
+        <v>506</v>
       </c>
       <c r="K27" t="s">
-        <v>247</v>
+        <v>506</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B28">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="F28" t="s">
-        <v>169</v>
+        <v>408</v>
       </c>
       <c r="G28" t="s">
-        <v>167</v>
+        <v>497</v>
       </c>
       <c r="H28" t="s">
-        <v>225</v>
+        <v>499</v>
       </c>
       <c r="I28" t="s">
-        <v>167</v>
+        <v>544</v>
       </c>
       <c r="J28" t="s">
-        <v>225</v>
+        <v>499</v>
       </c>
       <c r="K28" t="s">
-        <v>167</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B29">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>142</v>
+        <v>290</v>
       </c>
       <c r="F29" t="s">
-        <v>192</v>
+        <v>409</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>498</v>
       </c>
       <c r="H29" t="s">
-        <v>251</v>
+        <v>466</v>
       </c>
       <c r="I29" t="s">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="J29" t="s">
-        <v>262</v>
+        <v>436</v>
       </c>
       <c r="K29" t="s">
-        <v>167</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B30">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
-        <v>143</v>
+        <v>291</v>
       </c>
       <c r="F30" t="s">
-        <v>193</v>
+        <v>403</v>
       </c>
       <c r="G30" t="s">
-        <v>223</v>
+        <v>494</v>
       </c>
       <c r="H30" t="s">
-        <v>225</v>
+        <v>494</v>
       </c>
       <c r="I30" t="s">
-        <v>223</v>
+        <v>402</v>
       </c>
       <c r="J30" t="s">
-        <v>225</v>
+        <v>494</v>
       </c>
       <c r="K30" t="s">
-        <v>223</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>292</v>
       </c>
       <c r="F31" t="s">
-        <v>177</v>
+        <v>410</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="H31" t="s">
-        <v>252</v>
+        <v>505</v>
       </c>
       <c r="I31" t="s">
-        <v>177</v>
+        <v>388</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>452</v>
       </c>
       <c r="K31" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B32">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
+        <v>293</v>
       </c>
       <c r="F32" t="s">
-        <v>194</v>
+        <v>411</v>
       </c>
       <c r="G32" t="s">
-        <v>224</v>
+        <v>388</v>
       </c>
       <c r="H32" t="s">
-        <v>224</v>
+        <v>500</v>
       </c>
       <c r="I32" t="s">
-        <v>258</v>
+        <v>388</v>
       </c>
       <c r="J32" t="s">
-        <v>225</v>
+        <v>452</v>
       </c>
       <c r="K32" t="s">
-        <v>247</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B33">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="E33" t="s">
-        <v>146</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>412</v>
       </c>
       <c r="G33" t="s">
-        <v>225</v>
+        <v>499</v>
       </c>
       <c r="H33" t="s">
-        <v>225</v>
+        <v>531</v>
       </c>
       <c r="I33" t="s">
-        <v>169</v>
+        <v>499</v>
       </c>
       <c r="J33" t="s">
-        <v>225</v>
+        <v>486</v>
       </c>
       <c r="K33" t="s">
-        <v>167</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B34">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>147</v>
+        <v>295</v>
       </c>
       <c r="F34" t="s">
-        <v>181</v>
+        <v>413</v>
       </c>
       <c r="G34" t="s">
-        <v>217</v>
+        <v>500</v>
       </c>
       <c r="H34" t="s">
-        <v>180</v>
+        <v>452</v>
       </c>
       <c r="I34" t="s">
-        <v>181</v>
+        <v>500</v>
       </c>
       <c r="J34" t="s">
-        <v>195</v>
+        <v>452</v>
       </c>
       <c r="K34" t="s">
-        <v>217</v>
+        <v>452</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B35">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>148</v>
+        <v>296</v>
       </c>
       <c r="F35" t="s">
-        <v>195</v>
+        <v>414</v>
       </c>
       <c r="G35" t="s">
-        <v>225</v>
+        <v>494</v>
       </c>
       <c r="H35" t="s">
-        <v>225</v>
+        <v>500</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
       <c r="J35" t="s">
-        <v>225</v>
+        <v>452</v>
       </c>
       <c r="K35" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B36">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>415</v>
       </c>
       <c r="G36" t="s">
-        <v>226</v>
+        <v>501</v>
       </c>
       <c r="H36" t="s">
-        <v>226</v>
+        <v>402</v>
       </c>
       <c r="I36" t="s">
-        <v>196</v>
+        <v>501</v>
       </c>
       <c r="J36" t="s">
-        <v>230</v>
+        <v>402</v>
       </c>
       <c r="K36" t="s">
-        <v>247</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B37">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>150</v>
+        <v>298</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>401</v>
       </c>
       <c r="G37" t="s">
-        <v>227</v>
+        <v>492</v>
       </c>
       <c r="H37" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
       <c r="I37" t="s">
-        <v>167</v>
+        <v>401</v>
       </c>
       <c r="J37" t="s">
-        <v>171</v>
+        <v>433</v>
       </c>
       <c r="K37" t="s">
-        <v>167</v>
+        <v>492</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
-        <v>151</v>
+        <v>299</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>416</v>
       </c>
       <c r="G38" t="s">
-        <v>228</v>
+        <v>502</v>
       </c>
       <c r="H38" t="s">
-        <v>253</v>
+        <v>502</v>
       </c>
       <c r="I38" t="s">
-        <v>259</v>
+        <v>495</v>
       </c>
       <c r="J38" t="s">
-        <v>263</v>
+        <v>502</v>
       </c>
       <c r="K38" t="s">
-        <v>247</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B39">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>152</v>
+        <v>300</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>417</v>
       </c>
       <c r="G39" t="s">
-        <v>229</v>
+        <v>486</v>
       </c>
       <c r="H39" t="s">
-        <v>218</v>
+        <v>533</v>
       </c>
       <c r="I39" t="s">
-        <v>197</v>
+        <v>484</v>
       </c>
       <c r="J39" t="s">
-        <v>218</v>
+        <v>484</v>
       </c>
       <c r="K39" t="s">
-        <v>247</v>
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B40">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>153</v>
+        <v>301</v>
       </c>
       <c r="F40" t="s">
-        <v>198</v>
+        <v>418</v>
       </c>
       <c r="G40" t="s">
-        <v>218</v>
+        <v>486</v>
       </c>
       <c r="H40" t="s">
-        <v>218</v>
+        <v>458</v>
       </c>
       <c r="I40" t="s">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="J40" t="s">
-        <v>218</v>
+        <v>486</v>
       </c>
       <c r="K40" t="s">
-        <v>195</v>
+        <v>503</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B41">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
         <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>154</v>
+        <v>302</v>
       </c>
       <c r="F41" t="s">
-        <v>199</v>
+        <v>419</v>
       </c>
       <c r="G41" t="s">
-        <v>230</v>
+        <v>484</v>
       </c>
       <c r="H41" t="s">
-        <v>254</v>
+        <v>484</v>
       </c>
       <c r="I41" t="s">
-        <v>260</v>
+        <v>419</v>
       </c>
       <c r="J41" t="s">
-        <v>254</v>
+        <v>484</v>
       </c>
       <c r="K41" t="s">
-        <v>212</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B42">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
         <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="F42" t="s">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="G42" t="s">
-        <v>231</v>
+        <v>503</v>
       </c>
       <c r="H42" t="s">
-        <v>221</v>
+        <v>418</v>
       </c>
       <c r="I42" t="s">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>436</v>
       </c>
       <c r="K42" t="s">
-        <v>216</v>
+        <v>503</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B43">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
         <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
+        <v>304</v>
       </c>
       <c r="F43" t="s">
-        <v>201</v>
+        <v>421</v>
       </c>
       <c r="G43" t="s">
-        <v>232</v>
+        <v>504</v>
       </c>
       <c r="H43" t="s">
-        <v>232</v>
+        <v>534</v>
       </c>
       <c r="I43" t="s">
-        <v>201</v>
+        <v>421</v>
       </c>
       <c r="J43" t="s">
-        <v>221</v>
+        <v>504</v>
       </c>
       <c r="K43" t="s">
-        <v>167</v>
+        <v>503</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B44">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
         <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>305</v>
       </c>
       <c r="F44" t="s">
-        <v>184</v>
+        <v>422</v>
       </c>
       <c r="G44" t="s">
-        <v>233</v>
+        <v>497</v>
       </c>
       <c r="H44" t="s">
-        <v>255</v>
+        <v>423</v>
       </c>
       <c r="I44" t="s">
-        <v>234</v>
+        <v>497</v>
       </c>
       <c r="J44" t="s">
-        <v>218</v>
+        <v>498</v>
       </c>
       <c r="K44" t="s">
-        <v>211</v>
+        <v>497</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B45">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
         <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s">
-        <v>202</v>
+        <v>423</v>
       </c>
       <c r="G45" t="s">
-        <v>234</v>
+        <v>498</v>
       </c>
       <c r="H45" t="s">
-        <v>211</v>
+        <v>479</v>
       </c>
       <c r="I45" t="s">
-        <v>202</v>
+        <v>498</v>
       </c>
       <c r="J45" t="s">
-        <v>211</v>
+        <v>479</v>
       </c>
       <c r="K45" t="s">
-        <v>195</v>
+        <v>498</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B46">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
         <v>55</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="E46" t="s">
-        <v>159</v>
+        <v>307</v>
       </c>
       <c r="F46" t="s">
-        <v>171</v>
+        <v>424</v>
       </c>
       <c r="G46" t="s">
-        <v>210</v>
+        <v>505</v>
       </c>
       <c r="H46" t="s">
-        <v>171</v>
+        <v>505</v>
       </c>
       <c r="I46" t="s">
-        <v>256</v>
+        <v>498</v>
       </c>
       <c r="J46" t="s">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="K46" t="s">
-        <v>210</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B47">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C47" t="s">
         <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="E47" t="s">
-        <v>160</v>
+        <v>308</v>
       </c>
       <c r="F47" t="s">
-        <v>203</v>
+        <v>423</v>
       </c>
       <c r="G47" t="s">
-        <v>213</v>
+        <v>498</v>
       </c>
       <c r="H47" t="s">
-        <v>216</v>
+        <v>423</v>
       </c>
       <c r="I47" t="s">
-        <v>203</v>
+        <v>498</v>
       </c>
       <c r="J47" t="s">
-        <v>216</v>
+        <v>498</v>
       </c>
       <c r="K47" t="s">
-        <v>213</v>
+        <v>498</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B48">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
         <v>57</v>
       </c>
       <c r="D48" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="F48" t="s">
-        <v>204</v>
+        <v>425</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
+        <v>433</v>
       </c>
       <c r="H48" t="s">
-        <v>215</v>
+        <v>433</v>
       </c>
       <c r="I48" t="s">
-        <v>261</v>
+        <v>425</v>
       </c>
       <c r="J48" t="s">
-        <v>215</v>
+        <v>433</v>
       </c>
       <c r="K48" t="s">
-        <v>223</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B49">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
         <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="E49" t="s">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>205</v>
+        <v>426</v>
       </c>
       <c r="G49" t="s">
-        <v>236</v>
+        <v>501</v>
       </c>
       <c r="H49" t="s">
-        <v>254</v>
+        <v>535</v>
       </c>
       <c r="I49" t="s">
-        <v>262</v>
+        <v>501</v>
       </c>
       <c r="J49" t="s">
-        <v>254</v>
+        <v>494</v>
       </c>
       <c r="K49" t="s">
-        <v>262</v>
+        <v>501</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B50">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
         <v>59</v>
       </c>
       <c r="D50" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>311</v>
       </c>
       <c r="F50" t="s">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="G50" t="s">
-        <v>237</v>
+        <v>506</v>
       </c>
       <c r="H50" t="s">
-        <v>218</v>
+        <v>427</v>
       </c>
       <c r="I50" t="s">
-        <v>220</v>
+        <v>536</v>
       </c>
       <c r="J50" t="s">
-        <v>218</v>
+        <v>503</v>
       </c>
       <c r="K50" t="s">
-        <v>220</v>
+        <v>503</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
         <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
-        <v>164</v>
+        <v>312</v>
       </c>
       <c r="F51" t="s">
-        <v>184</v>
+        <v>428</v>
       </c>
       <c r="G51" t="s">
-        <v>229</v>
+        <v>506</v>
       </c>
       <c r="H51" t="s">
-        <v>233</v>
+        <v>536</v>
       </c>
       <c r="I51" t="s">
-        <v>255</v>
+        <v>428</v>
       </c>
       <c r="J51" t="s">
-        <v>211</v>
+        <v>503</v>
       </c>
       <c r="K51" t="s">
-        <v>218</v>
+        <v>506</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
         <v>61</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>313</v>
       </c>
       <c r="F52" t="s">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="G52" t="s">
-        <v>238</v>
+        <v>507</v>
       </c>
       <c r="H52" t="s">
-        <v>238</v>
+        <v>507</v>
       </c>
       <c r="I52" t="s">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="J52" t="s">
-        <v>247</v>
+        <v>507</v>
       </c>
       <c r="K52" t="s">
-        <v>195</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
         <v>62</v>
       </c>
       <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" t="s">
+        <v>430</v>
+      </c>
+      <c r="G53" t="s">
+        <v>492</v>
+      </c>
+      <c r="H53" t="s">
+        <v>492</v>
+      </c>
+      <c r="I53" t="s">
+        <v>430</v>
+      </c>
+      <c r="J53" t="s">
+        <v>492</v>
+      </c>
+      <c r="K53" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>2021</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" t="s">
+        <v>315</v>
+      </c>
+      <c r="F54" t="s">
+        <v>431</v>
+      </c>
+      <c r="G54" t="s">
+        <v>406</v>
+      </c>
+      <c r="H54" t="s">
+        <v>537</v>
+      </c>
+      <c r="I54" t="s">
+        <v>406</v>
+      </c>
+      <c r="J54" t="s">
+        <v>504</v>
+      </c>
+      <c r="K54" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>2021</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" t="s">
+        <v>316</v>
+      </c>
+      <c r="F55" t="s">
+        <v>432</v>
+      </c>
+      <c r="G55" t="s">
+        <v>501</v>
+      </c>
+      <c r="H55" t="s">
+        <v>432</v>
+      </c>
+      <c r="I55" t="s">
+        <v>415</v>
+      </c>
+      <c r="J55" t="s">
+        <v>501</v>
+      </c>
+      <c r="K55" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>2021</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" t="s">
+        <v>191</v>
+      </c>
+      <c r="E56" t="s">
+        <v>317</v>
+      </c>
+      <c r="F56" t="s">
+        <v>433</v>
+      </c>
+      <c r="G56" t="s">
+        <v>406</v>
+      </c>
+      <c r="H56" t="s">
+        <v>406</v>
+      </c>
+      <c r="I56" t="s">
+        <v>433</v>
+      </c>
+      <c r="J56" t="s">
+        <v>406</v>
+      </c>
+      <c r="K56" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>2021</v>
+      </c>
+      <c r="B57">
+        <v>31</v>
+      </c>
+      <c r="C57" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" t="s">
+        <v>192</v>
+      </c>
+      <c r="E57" t="s">
+        <v>318</v>
+      </c>
+      <c r="F57" t="s">
+        <v>434</v>
+      </c>
+      <c r="G57" t="s">
+        <v>508</v>
+      </c>
+      <c r="H57" t="s">
+        <v>519</v>
+      </c>
+      <c r="I57" t="s">
+        <v>479</v>
+      </c>
+      <c r="J57" t="s">
+        <v>504</v>
+      </c>
+      <c r="K57" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>2021</v>
+      </c>
+      <c r="B58">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" t="s">
+        <v>193</v>
+      </c>
+      <c r="E58" t="s">
+        <v>319</v>
+      </c>
+      <c r="F58" t="s">
+        <v>393</v>
+      </c>
+      <c r="G58" t="s">
+        <v>388</v>
+      </c>
+      <c r="H58" t="s">
+        <v>452</v>
+      </c>
+      <c r="I58" t="s">
+        <v>388</v>
+      </c>
+      <c r="J58" t="s">
+        <v>452</v>
+      </c>
+      <c r="K58" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59">
+        <v>57</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>194</v>
+      </c>
+      <c r="E59" t="s">
+        <v>320</v>
+      </c>
+      <c r="F59" t="s">
+        <v>435</v>
+      </c>
+      <c r="G59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H59" t="s">
+        <v>406</v>
+      </c>
+      <c r="I59" t="s">
+        <v>435</v>
+      </c>
+      <c r="J59" t="s">
+        <v>406</v>
+      </c>
+      <c r="K59" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>2021</v>
+      </c>
+      <c r="B60">
+        <v>69</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s">
+        <v>195</v>
+      </c>
+      <c r="E60" t="s">
+        <v>285</v>
+      </c>
+      <c r="F60" t="s">
+        <v>390</v>
+      </c>
+      <c r="G60" t="s">
+        <v>436</v>
+      </c>
+      <c r="H60" t="s">
+        <v>390</v>
+      </c>
+      <c r="I60" t="s">
+        <v>436</v>
+      </c>
+      <c r="J60" t="s">
+        <v>436</v>
+      </c>
+      <c r="K60" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>2021</v>
+      </c>
+      <c r="B61">
+        <v>74</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" t="s">
+        <v>321</v>
+      </c>
+      <c r="F61" t="s">
+        <v>436</v>
+      </c>
+      <c r="G61" t="s">
+        <v>510</v>
+      </c>
+      <c r="H61" t="s">
+        <v>538</v>
+      </c>
+      <c r="I61" t="s">
+        <v>436</v>
+      </c>
+      <c r="J61" t="s">
+        <v>436</v>
+      </c>
+      <c r="K61" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>2021</v>
+      </c>
+      <c r="B62">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>71</v>
+      </c>
+      <c r="D62" t="s">
+        <v>197</v>
+      </c>
+      <c r="E62" t="s">
+        <v>322</v>
+      </c>
+      <c r="F62" t="s">
+        <v>437</v>
+      </c>
+      <c r="G62" t="s">
+        <v>502</v>
+      </c>
+      <c r="H62" t="s">
+        <v>495</v>
+      </c>
+      <c r="I62" t="s">
+        <v>502</v>
+      </c>
+      <c r="J62" t="s">
+        <v>502</v>
+      </c>
+      <c r="K62" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>2021</v>
+      </c>
+      <c r="B63">
+        <v>118</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" t="s">
+        <v>198</v>
+      </c>
+      <c r="E63" t="s">
+        <v>323</v>
+      </c>
+      <c r="F63" t="s">
+        <v>404</v>
+      </c>
+      <c r="G63" t="s">
+        <v>494</v>
+      </c>
+      <c r="H63" t="s">
+        <v>404</v>
+      </c>
+      <c r="I63" t="s">
+        <v>494</v>
+      </c>
+      <c r="J63" t="s">
+        <v>494</v>
+      </c>
+      <c r="K63" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>2021</v>
+      </c>
+      <c r="B64">
+        <v>121</v>
+      </c>
+      <c r="C64" t="s">
+        <v>73</v>
+      </c>
+      <c r="D64" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" t="s">
+        <v>324</v>
+      </c>
+      <c r="F64" t="s">
+        <v>438</v>
+      </c>
+      <c r="G64" t="s">
+        <v>388</v>
+      </c>
+      <c r="H64" t="s">
+        <v>539</v>
+      </c>
+      <c r="I64" t="s">
+        <v>545</v>
+      </c>
+      <c r="J64" t="s">
+        <v>516</v>
+      </c>
+      <c r="K64" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>2021</v>
+      </c>
+      <c r="B65">
+        <v>122</v>
+      </c>
+      <c r="C65" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" t="s">
+        <v>200</v>
+      </c>
+      <c r="E65" t="s">
+        <v>325</v>
+      </c>
+      <c r="F65" t="s">
+        <v>439</v>
+      </c>
+      <c r="G65" t="s">
+        <v>484</v>
+      </c>
+      <c r="H65" t="s">
+        <v>402</v>
+      </c>
+      <c r="I65" t="s">
+        <v>439</v>
+      </c>
+      <c r="J65" t="s">
+        <v>402</v>
+      </c>
+      <c r="K65" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>2021</v>
+      </c>
+      <c r="B66">
+        <v>123</v>
+      </c>
+      <c r="C66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" t="s">
+        <v>326</v>
+      </c>
+      <c r="F66" t="s">
+        <v>403</v>
+      </c>
+      <c r="G66" t="s">
+        <v>402</v>
+      </c>
+      <c r="H66" t="s">
+        <v>403</v>
+      </c>
+      <c r="I66" t="s">
+        <v>402</v>
+      </c>
+      <c r="J66" t="s">
+        <v>402</v>
+      </c>
+      <c r="K66" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>2021</v>
+      </c>
+      <c r="B67">
+        <v>125</v>
+      </c>
+      <c r="C67" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" t="s">
+        <v>327</v>
+      </c>
+      <c r="F67" t="s">
+        <v>440</v>
+      </c>
+      <c r="G67" t="s">
+        <v>402</v>
+      </c>
+      <c r="H67" t="s">
+        <v>452</v>
+      </c>
+      <c r="I67" t="s">
+        <v>402</v>
+      </c>
+      <c r="J67" t="s">
+        <v>452</v>
+      </c>
+      <c r="K67" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>2021</v>
+      </c>
+      <c r="B68">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" t="s">
+        <v>328</v>
+      </c>
+      <c r="F68" t="s">
+        <v>441</v>
+      </c>
+      <c r="G68" t="s">
+        <v>497</v>
+      </c>
+      <c r="H68" t="s">
+        <v>497</v>
+      </c>
+      <c r="I68" t="s">
+        <v>544</v>
+      </c>
+      <c r="J68" t="s">
+        <v>497</v>
+      </c>
+      <c r="K68" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>2021</v>
+      </c>
+      <c r="B69">
+        <v>137</v>
+      </c>
+      <c r="C69" t="s">
+        <v>78</v>
+      </c>
+      <c r="D69" t="s">
+        <v>204</v>
+      </c>
+      <c r="E69" t="s">
+        <v>329</v>
+      </c>
+      <c r="F69" t="s">
+        <v>442</v>
+      </c>
+      <c r="G69" t="s">
+        <v>412</v>
+      </c>
+      <c r="H69" t="s">
+        <v>499</v>
+      </c>
+      <c r="I69" t="s">
+        <v>546</v>
+      </c>
+      <c r="J69" t="s">
+        <v>499</v>
+      </c>
+      <c r="K69" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>2021</v>
+      </c>
+      <c r="B70">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>205</v>
+      </c>
+      <c r="E70" t="s">
+        <v>330</v>
+      </c>
+      <c r="F70" t="s">
+        <v>443</v>
+      </c>
+      <c r="G70" t="s">
+        <v>511</v>
+      </c>
+      <c r="H70" t="s">
+        <v>408</v>
+      </c>
+      <c r="I70" t="s">
+        <v>443</v>
+      </c>
+      <c r="J70" t="s">
+        <v>408</v>
+      </c>
+      <c r="K70" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>2022</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" t="s">
+        <v>206</v>
+      </c>
+      <c r="E71" t="s">
+        <v>331</v>
+      </c>
+      <c r="F71" t="s">
+        <v>414</v>
+      </c>
+      <c r="G71" t="s">
+        <v>433</v>
+      </c>
+      <c r="H71" t="s">
+        <v>512</v>
+      </c>
+      <c r="I71" t="s">
+        <v>414</v>
+      </c>
+      <c r="J71" t="s">
+        <v>512</v>
+      </c>
+      <c r="K71" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>2022</v>
+      </c>
+      <c r="B72">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" t="s">
+        <v>332</v>
+      </c>
+      <c r="F72" t="s">
+        <v>444</v>
+      </c>
+      <c r="G72" t="s">
+        <v>512</v>
+      </c>
+      <c r="H72" t="s">
+        <v>512</v>
+      </c>
+      <c r="I72" t="s">
+        <v>444</v>
+      </c>
+      <c r="J72" t="s">
+        <v>512</v>
+      </c>
+      <c r="K72" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>2022</v>
+      </c>
+      <c r="B73">
+        <v>33</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>208</v>
+      </c>
+      <c r="E73" t="s">
+        <v>333</v>
+      </c>
+      <c r="F73" t="s">
+        <v>445</v>
+      </c>
+      <c r="G73" t="s">
+        <v>513</v>
+      </c>
+      <c r="H73" t="s">
+        <v>513</v>
+      </c>
+      <c r="I73" t="s">
+        <v>547</v>
+      </c>
+      <c r="J73" t="s">
+        <v>452</v>
+      </c>
+      <c r="K73" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>2022</v>
+      </c>
+      <c r="B74">
+        <v>35</v>
+      </c>
+      <c r="C74" t="s">
+        <v>83</v>
+      </c>
+      <c r="D74" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" t="s">
+        <v>334</v>
+      </c>
+      <c r="F74" t="s">
+        <v>446</v>
+      </c>
+      <c r="G74" t="s">
+        <v>514</v>
+      </c>
+      <c r="H74" t="s">
+        <v>452</v>
+      </c>
+      <c r="I74" t="s">
+        <v>446</v>
+      </c>
+      <c r="J74" t="s">
+        <v>452</v>
+      </c>
+      <c r="K74" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>2022</v>
+      </c>
+      <c r="B75">
+        <v>40</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" t="s">
+        <v>210</v>
+      </c>
+      <c r="E75" t="s">
+        <v>335</v>
+      </c>
+      <c r="F75" t="s">
+        <v>410</v>
+      </c>
+      <c r="G75" t="s">
+        <v>388</v>
+      </c>
+      <c r="H75" t="s">
+        <v>410</v>
+      </c>
+      <c r="I75" t="s">
+        <v>388</v>
+      </c>
+      <c r="J75" t="s">
+        <v>388</v>
+      </c>
+      <c r="K75" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>2022</v>
+      </c>
+      <c r="B76">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" t="s">
+        <v>336</v>
+      </c>
+      <c r="F76" t="s">
+        <v>393</v>
+      </c>
+      <c r="G76" t="s">
+        <v>452</v>
+      </c>
+      <c r="H76" t="s">
+        <v>452</v>
+      </c>
+      <c r="I76" t="s">
+        <v>393</v>
+      </c>
+      <c r="J76" t="s">
+        <v>452</v>
+      </c>
+      <c r="K76" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>2022</v>
+      </c>
+      <c r="B77">
+        <v>45</v>
+      </c>
+      <c r="C77" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" t="s">
+        <v>337</v>
+      </c>
+      <c r="F77" t="s">
+        <v>447</v>
+      </c>
+      <c r="G77" t="s">
+        <v>433</v>
+      </c>
+      <c r="H77" t="s">
+        <v>452</v>
+      </c>
+      <c r="I77" t="s">
+        <v>548</v>
+      </c>
+      <c r="J77" t="s">
+        <v>452</v>
+      </c>
+      <c r="K77" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>2022</v>
+      </c>
+      <c r="B78">
+        <v>46</v>
+      </c>
+      <c r="C78" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" t="s">
+        <v>213</v>
+      </c>
+      <c r="E78" t="s">
+        <v>338</v>
+      </c>
+      <c r="F78" t="s">
+        <v>448</v>
+      </c>
+      <c r="G78" t="s">
+        <v>406</v>
+      </c>
+      <c r="H78" t="s">
+        <v>406</v>
+      </c>
+      <c r="I78" t="s">
+        <v>448</v>
+      </c>
+      <c r="J78" t="s">
+        <v>406</v>
+      </c>
+      <c r="K78" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>2022</v>
+      </c>
+      <c r="B79">
+        <v>51</v>
+      </c>
+      <c r="C79" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" t="s">
+        <v>214</v>
+      </c>
+      <c r="E79" t="s">
+        <v>339</v>
+      </c>
+      <c r="F79" t="s">
+        <v>449</v>
+      </c>
+      <c r="G79" t="s">
+        <v>501</v>
+      </c>
+      <c r="H79" t="s">
+        <v>484</v>
+      </c>
+      <c r="I79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J79" t="s">
+        <v>484</v>
+      </c>
+      <c r="K79" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>2022</v>
+      </c>
+      <c r="B80">
+        <v>53</v>
+      </c>
+      <c r="C80" t="s">
+        <v>89</v>
+      </c>
+      <c r="D80" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" t="s">
+        <v>340</v>
+      </c>
+      <c r="F80" t="s">
+        <v>399</v>
+      </c>
+      <c r="G80" t="s">
+        <v>490</v>
+      </c>
+      <c r="H80" t="s">
+        <v>399</v>
+      </c>
+      <c r="I80" t="s">
+        <v>490</v>
+      </c>
+      <c r="J80" t="s">
+        <v>490</v>
+      </c>
+      <c r="K80" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>2022</v>
+      </c>
+      <c r="B81">
+        <v>55</v>
+      </c>
+      <c r="C81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" t="s">
+        <v>216</v>
+      </c>
+      <c r="E81" t="s">
+        <v>341</v>
+      </c>
+      <c r="F81" t="s">
+        <v>420</v>
+      </c>
+      <c r="G81" t="s">
+        <v>503</v>
+      </c>
+      <c r="H81" t="s">
+        <v>436</v>
+      </c>
+      <c r="I81" t="s">
+        <v>418</v>
+      </c>
+      <c r="J81" t="s">
+        <v>436</v>
+      </c>
+      <c r="K81" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>2022</v>
+      </c>
+      <c r="B82">
+        <v>59</v>
+      </c>
+      <c r="C82" t="s">
+        <v>91</v>
+      </c>
+      <c r="D82" t="s">
+        <v>217</v>
+      </c>
+      <c r="E82" t="s">
+        <v>342</v>
+      </c>
+      <c r="F82" t="s">
+        <v>427</v>
+      </c>
+      <c r="G82" t="s">
+        <v>515</v>
+      </c>
+      <c r="H82" t="s">
+        <v>503</v>
+      </c>
+      <c r="I82" t="s">
+        <v>427</v>
+      </c>
+      <c r="J82" t="s">
+        <v>503</v>
+      </c>
+      <c r="K82" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>2022</v>
+      </c>
+      <c r="B83">
+        <v>73</v>
+      </c>
+      <c r="C83" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" t="s">
+        <v>218</v>
+      </c>
+      <c r="E83" t="s">
+        <v>343</v>
+      </c>
+      <c r="F83" t="s">
+        <v>420</v>
+      </c>
+      <c r="G83" t="s">
+        <v>503</v>
+      </c>
+      <c r="H83" t="s">
+        <v>418</v>
+      </c>
+      <c r="I83" t="s">
+        <v>420</v>
+      </c>
+      <c r="J83" t="s">
+        <v>436</v>
+      </c>
+      <c r="K83" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>2022</v>
+      </c>
+      <c r="B84">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" t="s">
+        <v>219</v>
+      </c>
+      <c r="E84" t="s">
+        <v>344</v>
+      </c>
+      <c r="F84" t="s">
+        <v>450</v>
+      </c>
+      <c r="G84" t="s">
+        <v>516</v>
+      </c>
+      <c r="H84" t="s">
+        <v>523</v>
+      </c>
+      <c r="I84" t="s">
+        <v>516</v>
+      </c>
+      <c r="J84" t="s">
+        <v>516</v>
+      </c>
+      <c r="K84" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>2022</v>
+      </c>
+      <c r="B85">
+        <v>91</v>
+      </c>
+      <c r="C85" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" t="s">
+        <v>220</v>
+      </c>
+      <c r="E85" t="s">
+        <v>345</v>
+      </c>
+      <c r="F85" t="s">
+        <v>451</v>
+      </c>
+      <c r="G85" t="s">
+        <v>484</v>
+      </c>
+      <c r="H85" t="s">
+        <v>451</v>
+      </c>
+      <c r="I85" t="s">
+        <v>484</v>
+      </c>
+      <c r="J85" t="s">
+        <v>484</v>
+      </c>
+      <c r="K85" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>2022</v>
+      </c>
+      <c r="B86">
+        <v>99</v>
+      </c>
+      <c r="C86" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" t="s">
+        <v>221</v>
+      </c>
+      <c r="E86" t="s">
+        <v>346</v>
+      </c>
+      <c r="F86" t="s">
+        <v>452</v>
+      </c>
+      <c r="G86" t="s">
+        <v>517</v>
+      </c>
+      <c r="H86" t="s">
+        <v>452</v>
+      </c>
+      <c r="I86" t="s">
+        <v>517</v>
+      </c>
+      <c r="J86" t="s">
+        <v>452</v>
+      </c>
+      <c r="K86" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>2022</v>
+      </c>
+      <c r="B87">
+        <v>100</v>
+      </c>
+      <c r="C87" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" t="s">
+        <v>347</v>
+      </c>
+      <c r="F87" t="s">
+        <v>453</v>
+      </c>
+      <c r="G87" t="s">
+        <v>388</v>
+      </c>
+      <c r="H87" t="s">
+        <v>516</v>
+      </c>
+      <c r="I87" t="s">
+        <v>550</v>
+      </c>
+      <c r="J87" t="s">
+        <v>516</v>
+      </c>
+      <c r="K87" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>2022</v>
+      </c>
+      <c r="B88">
+        <v>102</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>348</v>
+      </c>
+      <c r="F88" t="s">
+        <v>436</v>
+      </c>
+      <c r="G88" t="s">
+        <v>452</v>
+      </c>
+      <c r="H88" t="s">
+        <v>452</v>
+      </c>
+      <c r="I88" t="s">
+        <v>436</v>
+      </c>
+      <c r="J88" t="s">
+        <v>452</v>
+      </c>
+      <c r="K88" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>2022</v>
+      </c>
+      <c r="B89">
+        <v>103</v>
+      </c>
+      <c r="C89" t="s">
+        <v>98</v>
+      </c>
+      <c r="D89" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" t="s">
+        <v>349</v>
+      </c>
+      <c r="F89" t="s">
+        <v>454</v>
+      </c>
+      <c r="G89" t="s">
+        <v>504</v>
+      </c>
+      <c r="H89" t="s">
+        <v>504</v>
+      </c>
+      <c r="I89" t="s">
+        <v>454</v>
+      </c>
+      <c r="J89" t="s">
+        <v>504</v>
+      </c>
+      <c r="K89" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>2022</v>
+      </c>
+      <c r="B90">
+        <v>105</v>
+      </c>
+      <c r="C90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>350</v>
+      </c>
+      <c r="F90" t="s">
+        <v>455</v>
+      </c>
+      <c r="G90" t="s">
+        <v>476</v>
+      </c>
+      <c r="H90" t="s">
+        <v>476</v>
+      </c>
+      <c r="I90" t="s">
+        <v>455</v>
+      </c>
+      <c r="J90" t="s">
+        <v>502</v>
+      </c>
+      <c r="K90" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>2022</v>
+      </c>
+      <c r="B91">
+        <v>111</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91" t="s">
+        <v>226</v>
+      </c>
+      <c r="E91" t="s">
+        <v>351</v>
+      </c>
+      <c r="F91" t="s">
+        <v>456</v>
+      </c>
+      <c r="G91" t="s">
+        <v>498</v>
+      </c>
+      <c r="H91" t="s">
+        <v>498</v>
+      </c>
+      <c r="I91" t="s">
+        <v>456</v>
+      </c>
+      <c r="J91" t="s">
+        <v>498</v>
+      </c>
+      <c r="K91" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92">
+        <v>2022</v>
+      </c>
+      <c r="B92">
+        <v>128</v>
+      </c>
+      <c r="C92" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" t="s">
+        <v>227</v>
+      </c>
+      <c r="E92" t="s">
+        <v>352</v>
+      </c>
+      <c r="F92" t="s">
+        <v>387</v>
+      </c>
+      <c r="G92" t="s">
+        <v>434</v>
+      </c>
+      <c r="H92" t="s">
+        <v>479</v>
+      </c>
+      <c r="I92" t="s">
+        <v>387</v>
+      </c>
+      <c r="J92" t="s">
+        <v>479</v>
+      </c>
+      <c r="K92" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93">
+        <v>2022</v>
+      </c>
+      <c r="B93">
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>102</v>
+      </c>
+      <c r="D93" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" t="s">
+        <v>353</v>
+      </c>
+      <c r="F93" t="s">
+        <v>413</v>
+      </c>
+      <c r="G93" t="s">
+        <v>494</v>
+      </c>
+      <c r="H93" t="s">
+        <v>404</v>
+      </c>
+      <c r="I93" t="s">
+        <v>494</v>
+      </c>
+      <c r="J93" t="s">
+        <v>494</v>
+      </c>
+      <c r="K93" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94">
+        <v>2022</v>
+      </c>
+      <c r="B94">
+        <v>138</v>
+      </c>
+      <c r="C94" t="s">
+        <v>103</v>
+      </c>
+      <c r="D94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" t="s">
+        <v>354</v>
+      </c>
+      <c r="F94" t="s">
+        <v>408</v>
+      </c>
+      <c r="G94" t="s">
+        <v>443</v>
+      </c>
+      <c r="H94" t="s">
+        <v>408</v>
+      </c>
+      <c r="I94" t="s">
+        <v>388</v>
+      </c>
+      <c r="J94" t="s">
+        <v>408</v>
+      </c>
+      <c r="K94" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95">
+        <v>2023</v>
+      </c>
+      <c r="B95">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>104</v>
+      </c>
+      <c r="D95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" t="s">
+        <v>355</v>
+      </c>
+      <c r="F95" t="s">
+        <v>434</v>
+      </c>
+      <c r="G95" t="s">
+        <v>507</v>
+      </c>
+      <c r="H95" t="s">
+        <v>540</v>
+      </c>
+      <c r="I95" t="s">
+        <v>387</v>
+      </c>
+      <c r="J95" t="s">
+        <v>484</v>
+      </c>
+      <c r="K95" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96">
+        <v>2023</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="s">
+        <v>105</v>
+      </c>
+      <c r="D96" t="s">
+        <v>231</v>
+      </c>
+      <c r="E96" t="s">
+        <v>356</v>
+      </c>
+      <c r="F96" t="s">
+        <v>457</v>
+      </c>
+      <c r="G96" t="s">
+        <v>518</v>
+      </c>
+      <c r="H96" t="s">
+        <v>484</v>
+      </c>
+      <c r="I96" t="s">
+        <v>551</v>
+      </c>
+      <c r="J96" t="s">
+        <v>484</v>
+      </c>
+      <c r="K96" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97">
+        <v>2023</v>
+      </c>
+      <c r="B97">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>232</v>
+      </c>
+      <c r="E97" t="s">
+        <v>301</v>
+      </c>
+      <c r="F97" t="s">
+        <v>458</v>
+      </c>
+      <c r="G97" t="s">
+        <v>486</v>
+      </c>
+      <c r="H97" t="s">
+        <v>486</v>
+      </c>
+      <c r="I97" t="s">
+        <v>458</v>
+      </c>
+      <c r="J97" t="s">
+        <v>486</v>
+      </c>
+      <c r="K97" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98">
+        <v>2023</v>
+      </c>
+      <c r="B98">
+        <v>15</v>
+      </c>
+      <c r="C98" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" t="s">
+        <v>233</v>
+      </c>
+      <c r="E98" t="s">
+        <v>357</v>
+      </c>
+      <c r="F98" t="s">
+        <v>459</v>
+      </c>
+      <c r="G98" t="s">
+        <v>519</v>
+      </c>
+      <c r="H98" t="s">
+        <v>504</v>
+      </c>
+      <c r="I98" t="s">
+        <v>519</v>
+      </c>
+      <c r="J98" t="s">
+        <v>504</v>
+      </c>
+      <c r="K98" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99">
+        <v>2023</v>
+      </c>
+      <c r="B99">
+        <v>16</v>
+      </c>
+      <c r="C99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" t="s">
+        <v>234</v>
+      </c>
+      <c r="E99" t="s">
+        <v>358</v>
+      </c>
+      <c r="F99" t="s">
+        <v>459</v>
+      </c>
+      <c r="G99" t="s">
+        <v>519</v>
+      </c>
+      <c r="H99" t="s">
+        <v>504</v>
+      </c>
+      <c r="I99" t="s">
+        <v>459</v>
+      </c>
+      <c r="J99" t="s">
+        <v>504</v>
+      </c>
+      <c r="K99" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100">
+        <v>2023</v>
+      </c>
+      <c r="B100">
+        <v>22</v>
+      </c>
+      <c r="C100" t="s">
+        <v>109</v>
+      </c>
+      <c r="D100" t="s">
+        <v>235</v>
+      </c>
+      <c r="E100" t="s">
+        <v>359</v>
+      </c>
+      <c r="F100" t="s">
+        <v>460</v>
+      </c>
+      <c r="G100" t="s">
+        <v>504</v>
+      </c>
+      <c r="H100" t="s">
+        <v>504</v>
+      </c>
+      <c r="I100" t="s">
+        <v>390</v>
+      </c>
+      <c r="J100" t="s">
+        <v>504</v>
+      </c>
+      <c r="K100" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101">
+        <v>2023</v>
+      </c>
+      <c r="B101">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" t="s">
+        <v>236</v>
+      </c>
+      <c r="E101" t="s">
+        <v>360</v>
+      </c>
+      <c r="F101" t="s">
+        <v>420</v>
+      </c>
+      <c r="G101" t="s">
+        <v>503</v>
+      </c>
+      <c r="H101" t="s">
+        <v>503</v>
+      </c>
+      <c r="I101" t="s">
+        <v>420</v>
+      </c>
+      <c r="J101" t="s">
+        <v>503</v>
+      </c>
+      <c r="K101" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102">
+        <v>2023</v>
+      </c>
+      <c r="B102">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>111</v>
+      </c>
+      <c r="D102" t="s">
+        <v>237</v>
+      </c>
+      <c r="E102" t="s">
+        <v>361</v>
+      </c>
+      <c r="F102" t="s">
+        <v>392</v>
+      </c>
+      <c r="G102" t="s">
+        <v>483</v>
+      </c>
+      <c r="H102" t="s">
+        <v>541</v>
+      </c>
+      <c r="I102" t="s">
+        <v>392</v>
+      </c>
+      <c r="J102" t="s">
+        <v>541</v>
+      </c>
+      <c r="K102" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103">
+        <v>2023</v>
+      </c>
+      <c r="B103">
+        <v>48</v>
+      </c>
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" t="s">
+        <v>238</v>
+      </c>
+      <c r="E103" t="s">
+        <v>362</v>
+      </c>
+      <c r="F103" t="s">
+        <v>461</v>
+      </c>
+      <c r="G103" t="s">
+        <v>435</v>
+      </c>
+      <c r="H103" t="s">
+        <v>406</v>
+      </c>
+      <c r="I103" t="s">
+        <v>435</v>
+      </c>
+      <c r="J103" t="s">
+        <v>406</v>
+      </c>
+      <c r="K103" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104">
+        <v>2023</v>
+      </c>
+      <c r="B104">
+        <v>51</v>
+      </c>
+      <c r="C104" t="s">
+        <v>113</v>
+      </c>
+      <c r="D104" t="s">
+        <v>239</v>
+      </c>
+      <c r="E104" t="s">
+        <v>363</v>
+      </c>
+      <c r="F104" t="s">
+        <v>462</v>
+      </c>
+      <c r="G104" t="s">
+        <v>502</v>
+      </c>
+      <c r="H104" t="s">
+        <v>491</v>
+      </c>
+      <c r="I104" t="s">
+        <v>552</v>
+      </c>
+      <c r="J104" t="s">
+        <v>491</v>
+      </c>
+      <c r="K104" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105">
+        <v>2023</v>
+      </c>
+      <c r="B105">
+        <v>78</v>
+      </c>
+      <c r="C105" t="s">
         <v>114</v>
       </c>
-      <c r="E53" t="s">
-        <v>166</v>
-      </c>
-      <c r="F53" t="s">
-        <v>170</v>
-      </c>
-      <c r="G53" t="s">
-        <v>198</v>
-      </c>
-      <c r="H53" t="s">
-        <v>198</v>
-      </c>
-      <c r="I53" t="s">
-        <v>170</v>
-      </c>
-      <c r="J53" t="s">
-        <v>218</v>
-      </c>
-      <c r="K53" t="s">
-        <v>195</v>
+      <c r="D105" t="s">
+        <v>240</v>
+      </c>
+      <c r="E105" t="s">
+        <v>364</v>
+      </c>
+      <c r="F105" t="s">
+        <v>463</v>
+      </c>
+      <c r="G105" t="s">
+        <v>520</v>
+      </c>
+      <c r="H105" t="s">
+        <v>406</v>
+      </c>
+      <c r="I105" t="s">
+        <v>463</v>
+      </c>
+      <c r="J105" t="s">
+        <v>406</v>
+      </c>
+      <c r="K105" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106">
+        <v>2023</v>
+      </c>
+      <c r="B106">
+        <v>80</v>
+      </c>
+      <c r="C106" t="s">
+        <v>115</v>
+      </c>
+      <c r="D106" t="s">
+        <v>241</v>
+      </c>
+      <c r="E106" t="s">
+        <v>365</v>
+      </c>
+      <c r="F106" t="s">
+        <v>464</v>
+      </c>
+      <c r="G106" t="s">
+        <v>521</v>
+      </c>
+      <c r="H106" t="s">
+        <v>521</v>
+      </c>
+      <c r="I106" t="s">
+        <v>464</v>
+      </c>
+      <c r="J106" t="s">
+        <v>406</v>
+      </c>
+      <c r="K106" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107">
+        <v>2023</v>
+      </c>
+      <c r="B107">
+        <v>93</v>
+      </c>
+      <c r="C107" t="s">
+        <v>116</v>
+      </c>
+      <c r="D107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E107" t="s">
+        <v>366</v>
+      </c>
+      <c r="F107" t="s">
+        <v>465</v>
+      </c>
+      <c r="G107" t="s">
+        <v>479</v>
+      </c>
+      <c r="H107" t="s">
+        <v>459</v>
+      </c>
+      <c r="I107" t="s">
+        <v>465</v>
+      </c>
+      <c r="J107" t="s">
+        <v>479</v>
+      </c>
+      <c r="K107" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108">
+        <v>2023</v>
+      </c>
+      <c r="B108">
+        <v>106</v>
+      </c>
+      <c r="C108" t="s">
+        <v>117</v>
+      </c>
+      <c r="D108" t="s">
+        <v>243</v>
+      </c>
+      <c r="E108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F108" t="s">
+        <v>423</v>
+      </c>
+      <c r="G108" t="s">
+        <v>522</v>
+      </c>
+      <c r="H108" t="s">
+        <v>542</v>
+      </c>
+      <c r="I108" t="s">
+        <v>456</v>
+      </c>
+      <c r="J108" t="s">
+        <v>504</v>
+      </c>
+      <c r="K108" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109">
+        <v>2023</v>
+      </c>
+      <c r="B109">
+        <v>107</v>
+      </c>
+      <c r="C109" t="s">
+        <v>118</v>
+      </c>
+      <c r="D109" t="s">
+        <v>244</v>
+      </c>
+      <c r="E109" t="s">
+        <v>368</v>
+      </c>
+      <c r="F109" t="s">
+        <v>466</v>
+      </c>
+      <c r="G109" t="s">
+        <v>456</v>
+      </c>
+      <c r="H109" t="s">
+        <v>498</v>
+      </c>
+      <c r="I109" t="s">
+        <v>466</v>
+      </c>
+      <c r="J109" t="s">
+        <v>498</v>
+      </c>
+      <c r="K109" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110">
+        <v>2023</v>
+      </c>
+      <c r="B110">
+        <v>108</v>
+      </c>
+      <c r="C110" t="s">
+        <v>119</v>
+      </c>
+      <c r="D110" t="s">
+        <v>245</v>
+      </c>
+      <c r="E110" t="s">
+        <v>369</v>
+      </c>
+      <c r="F110" t="s">
+        <v>467</v>
+      </c>
+      <c r="G110" t="s">
+        <v>523</v>
+      </c>
+      <c r="H110" t="s">
+        <v>498</v>
+      </c>
+      <c r="I110" t="s">
+        <v>467</v>
+      </c>
+      <c r="J110" t="s">
+        <v>498</v>
+      </c>
+      <c r="K110" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111">
+        <v>2023</v>
+      </c>
+      <c r="B111">
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>246</v>
+      </c>
+      <c r="E111" t="s">
+        <v>370</v>
+      </c>
+      <c r="F111" t="s">
+        <v>468</v>
+      </c>
+      <c r="G111" t="s">
+        <v>479</v>
+      </c>
+      <c r="H111" t="s">
+        <v>541</v>
+      </c>
+      <c r="I111" t="s">
+        <v>553</v>
+      </c>
+      <c r="J111" t="s">
+        <v>541</v>
+      </c>
+      <c r="K111" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112">
+        <v>2023</v>
+      </c>
+      <c r="B112">
+        <v>114</v>
+      </c>
+      <c r="C112" t="s">
+        <v>121</v>
+      </c>
+      <c r="D112" t="s">
+        <v>247</v>
+      </c>
+      <c r="E112" t="s">
+        <v>371</v>
+      </c>
+      <c r="F112" t="s">
+        <v>469</v>
+      </c>
+      <c r="G112" t="s">
+        <v>406</v>
+      </c>
+      <c r="H112" t="s">
+        <v>406</v>
+      </c>
+      <c r="I112" t="s">
+        <v>469</v>
+      </c>
+      <c r="J112" t="s">
+        <v>406</v>
+      </c>
+      <c r="K112" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113">
+        <v>2023</v>
+      </c>
+      <c r="B113">
+        <v>117</v>
+      </c>
+      <c r="C113" t="s">
+        <v>122</v>
+      </c>
+      <c r="D113" t="s">
+        <v>248</v>
+      </c>
+      <c r="E113" t="s">
+        <v>372</v>
+      </c>
+      <c r="F113" t="s">
+        <v>470</v>
+      </c>
+      <c r="G113" t="s">
+        <v>507</v>
+      </c>
+      <c r="H113" t="s">
+        <v>503</v>
+      </c>
+      <c r="I113" t="s">
+        <v>461</v>
+      </c>
+      <c r="J113" t="s">
+        <v>503</v>
+      </c>
+      <c r="K113" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114">
+        <v>2023</v>
+      </c>
+      <c r="B114">
+        <v>120</v>
+      </c>
+      <c r="C114" t="s">
+        <v>123</v>
+      </c>
+      <c r="D114" t="s">
+        <v>249</v>
+      </c>
+      <c r="E114" t="s">
+        <v>373</v>
+      </c>
+      <c r="F114" t="s">
+        <v>408</v>
+      </c>
+      <c r="G114" t="s">
+        <v>497</v>
+      </c>
+      <c r="H114" t="s">
+        <v>408</v>
+      </c>
+      <c r="I114" t="s">
+        <v>544</v>
+      </c>
+      <c r="J114" t="s">
+        <v>408</v>
+      </c>
+      <c r="K114" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115">
+        <v>2023</v>
+      </c>
+      <c r="B115">
+        <v>123</v>
+      </c>
+      <c r="C115" t="s">
+        <v>124</v>
+      </c>
+      <c r="D115" t="s">
+        <v>250</v>
+      </c>
+      <c r="E115" t="s">
+        <v>374</v>
+      </c>
+      <c r="F115" t="s">
+        <v>471</v>
+      </c>
+      <c r="G115" t="s">
+        <v>499</v>
+      </c>
+      <c r="H115" t="s">
+        <v>486</v>
+      </c>
+      <c r="I115" t="s">
+        <v>471</v>
+      </c>
+      <c r="J115" t="s">
+        <v>486</v>
+      </c>
+      <c r="K115" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116">
+        <v>2023</v>
+      </c>
+      <c r="B116">
+        <v>131</v>
+      </c>
+      <c r="C116" t="s">
+        <v>125</v>
+      </c>
+      <c r="D116" t="s">
+        <v>251</v>
+      </c>
+      <c r="E116" t="s">
+        <v>375</v>
+      </c>
+      <c r="F116" t="s">
+        <v>472</v>
+      </c>
+      <c r="G116" t="s">
+        <v>524</v>
+      </c>
+      <c r="H116" t="s">
+        <v>492</v>
+      </c>
+      <c r="I116" t="s">
+        <v>554</v>
+      </c>
+      <c r="J116" t="s">
+        <v>492</v>
+      </c>
+      <c r="K116" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117">
+        <v>2024</v>
+      </c>
+      <c r="B117">
+        <v>101</v>
+      </c>
+      <c r="C117" t="s">
+        <v>126</v>
+      </c>
+      <c r="D117" t="s">
+        <v>252</v>
+      </c>
+      <c r="E117" t="s">
+        <v>376</v>
+      </c>
+      <c r="F117" t="s">
+        <v>473</v>
+      </c>
+      <c r="G117" t="s">
+        <v>525</v>
+      </c>
+      <c r="H117" t="s">
+        <v>491</v>
+      </c>
+      <c r="I117" t="s">
+        <v>516</v>
+      </c>
+      <c r="J117" t="s">
+        <v>491</v>
+      </c>
+      <c r="K117" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118">
+        <v>2024</v>
+      </c>
+      <c r="B118">
+        <v>105</v>
+      </c>
+      <c r="C118" t="s">
+        <v>127</v>
+      </c>
+      <c r="D118" t="s">
+        <v>253</v>
+      </c>
+      <c r="E118" t="s">
+        <v>377</v>
+      </c>
+      <c r="F118" t="s">
+        <v>455</v>
+      </c>
+      <c r="G118" t="s">
+        <v>479</v>
+      </c>
+      <c r="H118" t="s">
+        <v>502</v>
+      </c>
+      <c r="I118" t="s">
+        <v>476</v>
+      </c>
+      <c r="J118" t="s">
+        <v>502</v>
+      </c>
+      <c r="K118" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119">
+        <v>2024</v>
+      </c>
+      <c r="B119">
+        <v>112</v>
+      </c>
+      <c r="C119" t="s">
+        <v>128</v>
+      </c>
+      <c r="D119" t="s">
+        <v>254</v>
+      </c>
+      <c r="E119" t="s">
+        <v>378</v>
+      </c>
+      <c r="F119" t="s">
+        <v>474</v>
+      </c>
+      <c r="G119" t="s">
+        <v>436</v>
+      </c>
+      <c r="H119" t="s">
+        <v>516</v>
+      </c>
+      <c r="I119" t="s">
+        <v>555</v>
+      </c>
+      <c r="J119" t="s">
+        <v>516</v>
+      </c>
+      <c r="K119" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120">
+        <v>2024</v>
+      </c>
+      <c r="B120">
+        <v>113</v>
+      </c>
+      <c r="C120" t="s">
+        <v>129</v>
+      </c>
+      <c r="D120" t="s">
+        <v>255</v>
+      </c>
+      <c r="E120" t="s">
+        <v>379</v>
+      </c>
+      <c r="F120" t="s">
+        <v>415</v>
+      </c>
+      <c r="G120" t="s">
+        <v>414</v>
+      </c>
+      <c r="H120" t="s">
+        <v>433</v>
+      </c>
+      <c r="I120" t="s">
+        <v>415</v>
+      </c>
+      <c r="J120" t="s">
+        <v>433</v>
+      </c>
+      <c r="K120" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121">
+        <v>2024</v>
+      </c>
+      <c r="B121">
+        <v>131</v>
+      </c>
+      <c r="C121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D121" t="s">
+        <v>256</v>
+      </c>
+      <c r="E121" t="s">
+        <v>380</v>
+      </c>
+      <c r="F121" t="s">
+        <v>475</v>
+      </c>
+      <c r="G121" t="s">
+        <v>526</v>
+      </c>
+      <c r="H121" t="s">
+        <v>504</v>
+      </c>
+      <c r="I121" t="s">
+        <v>506</v>
+      </c>
+      <c r="J121" t="s">
+        <v>504</v>
+      </c>
+      <c r="K121" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122">
+        <v>2024</v>
+      </c>
+      <c r="B122">
+        <v>139</v>
+      </c>
+      <c r="C122" t="s">
+        <v>131</v>
+      </c>
+      <c r="D122" t="s">
+        <v>257</v>
+      </c>
+      <c r="E122" t="s">
+        <v>381</v>
+      </c>
+      <c r="F122" t="s">
+        <v>476</v>
+      </c>
+      <c r="G122" t="s">
+        <v>455</v>
+      </c>
+      <c r="H122" t="s">
+        <v>502</v>
+      </c>
+      <c r="I122" t="s">
+        <v>476</v>
+      </c>
+      <c r="J122" t="s">
+        <v>502</v>
+      </c>
+      <c r="K122" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123">
+        <v>2025</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>132</v>
+      </c>
+      <c r="D123" t="s">
+        <v>258</v>
+      </c>
+      <c r="E123" t="s">
+        <v>382</v>
+      </c>
+      <c r="F123" t="s">
+        <v>423</v>
+      </c>
+      <c r="G123" t="s">
+        <v>519</v>
+      </c>
+      <c r="H123" t="s">
+        <v>522</v>
+      </c>
+      <c r="I123" t="s">
+        <v>542</v>
+      </c>
+      <c r="J123" t="s">
+        <v>498</v>
+      </c>
+      <c r="K123" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124">
+        <v>2025</v>
+      </c>
+      <c r="B124">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>133</v>
+      </c>
+      <c r="D124" t="s">
+        <v>259</v>
+      </c>
+      <c r="E124" t="s">
+        <v>383</v>
+      </c>
+      <c r="F124" t="s">
+        <v>477</v>
+      </c>
+      <c r="G124" t="s">
+        <v>465</v>
+      </c>
+      <c r="H124" t="s">
+        <v>465</v>
+      </c>
+      <c r="I124" t="s">
+        <v>477</v>
+      </c>
+      <c r="J124" t="s">
+        <v>479</v>
+      </c>
+      <c r="K124" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125">
+        <v>2025</v>
+      </c>
+      <c r="B125">
+        <v>7</v>
+      </c>
+      <c r="C125" t="s">
+        <v>134</v>
+      </c>
+      <c r="D125" t="s">
+        <v>260</v>
+      </c>
+      <c r="E125" t="s">
+        <v>384</v>
+      </c>
+      <c r="F125" t="s">
+        <v>477</v>
+      </c>
+      <c r="G125" t="s">
+        <v>465</v>
+      </c>
+      <c r="H125" t="s">
+        <v>436</v>
+      </c>
+      <c r="I125" t="s">
+        <v>477</v>
+      </c>
+      <c r="J125" t="s">
+        <v>436</v>
+      </c>
+      <c r="K125" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126">
+        <v>2025</v>
+      </c>
+      <c r="B126">
+        <v>8</v>
+      </c>
+      <c r="C126" t="s">
+        <v>135</v>
+      </c>
+      <c r="D126" t="s">
+        <v>261</v>
+      </c>
+      <c r="E126" t="s">
+        <v>385</v>
+      </c>
+      <c r="F126" t="s">
+        <v>390</v>
+      </c>
+      <c r="G126" t="s">
+        <v>460</v>
+      </c>
+      <c r="H126" t="s">
+        <v>460</v>
+      </c>
+      <c r="I126" t="s">
+        <v>390</v>
+      </c>
+      <c r="J126" t="s">
+        <v>504</v>
+      </c>
+      <c r="K126" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127">
+        <v>2025</v>
+      </c>
+      <c r="B127">
+        <v>60</v>
+      </c>
+      <c r="C127" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" t="s">
+        <v>262</v>
+      </c>
+      <c r="E127" t="s">
+        <v>386</v>
+      </c>
+      <c r="F127" t="s">
+        <v>478</v>
+      </c>
+      <c r="G127" t="s">
+        <v>438</v>
+      </c>
+      <c r="H127" t="s">
+        <v>402</v>
+      </c>
+      <c r="I127" t="s">
+        <v>438</v>
+      </c>
+      <c r="J127" t="s">
+        <v>402</v>
+      </c>
+      <c r="K127" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/Question_Classification/results/expert_review/reviewer_discordances.xlsx
+++ b/Question_Classification/results/expert_review/reviewer_discordances.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filow\OneDrive\Desktop\Repository\ITAMed\Question_Classification\results\expert_review\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B25E827-B10E-48C2-AED7-BF94F520CE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="16230" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1687,8 +1693,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1747,17 +1753,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1795,7 +1809,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1829,6 +1843,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1863,9 +1878,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2038,11 +2054,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K127"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="8" max="9" width="65.20703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="37.68359375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2077,7 +2097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>2017</v>
       </c>
@@ -2112,7 +2132,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2017</v>
       </c>
@@ -2147,7 +2167,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2017</v>
       </c>
@@ -2182,7 +2202,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>2017</v>
       </c>
@@ -2217,7 +2237,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -2252,7 +2272,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>2017</v>
       </c>
@@ -2287,7 +2307,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>2017</v>
       </c>
@@ -2322,7 +2342,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>2017</v>
       </c>
@@ -2357,7 +2377,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>2017</v>
       </c>
@@ -2392,7 +2412,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>2017</v>
       </c>
@@ -2427,7 +2447,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>2017</v>
       </c>
@@ -2462,7 +2482,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>2017</v>
       </c>
@@ -2497,7 +2517,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -2532,7 +2552,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>2017</v>
       </c>
@@ -2567,7 +2587,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>2017</v>
       </c>
@@ -2602,7 +2622,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>2017</v>
       </c>
@@ -2637,7 +2657,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>2017</v>
       </c>
@@ -2672,7 +2692,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>2017</v>
       </c>
@@ -2707,7 +2727,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>2018</v>
       </c>
@@ -2742,7 +2762,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -2777,7 +2797,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>2018</v>
       </c>
@@ -2812,7 +2832,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>2018</v>
       </c>
@@ -2847,7 +2867,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>2018</v>
       </c>
@@ -2882,7 +2902,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>2018</v>
       </c>
@@ -2917,7 +2937,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>2018</v>
       </c>
@@ -2952,7 +2972,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>2018</v>
       </c>
@@ -2987,7 +3007,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>2018</v>
       </c>
@@ -3022,7 +3042,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>2018</v>
       </c>
@@ -3057,7 +3077,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>2018</v>
       </c>
@@ -3092,7 +3112,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>2018</v>
       </c>
@@ -3127,7 +3147,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -3162,7 +3182,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>2018</v>
       </c>
@@ -3197,7 +3217,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>2018</v>
       </c>
@@ -3232,7 +3252,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>2018</v>
       </c>
@@ -3267,7 +3287,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>2018</v>
       </c>
@@ -3302,7 +3322,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>2018</v>
       </c>
@@ -3337,7 +3357,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2018</v>
       </c>
@@ -3372,7 +3392,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>2018</v>
       </c>
@@ -3407,7 +3427,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>2018</v>
       </c>
@@ -3442,7 +3462,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>2018</v>
       </c>
@@ -3477,7 +3497,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>2018</v>
       </c>
@@ -3512,7 +3532,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>2018</v>
       </c>
@@ -3547,7 +3567,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>2018</v>
       </c>
@@ -3582,7 +3602,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>2018</v>
       </c>
@@ -3617,7 +3637,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>2018</v>
       </c>
@@ -3652,7 +3672,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>2018</v>
       </c>
@@ -3687,7 +3707,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>2018</v>
       </c>
@@ -3722,7 +3742,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>2020</v>
       </c>
@@ -3757,7 +3777,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>2020</v>
       </c>
@@ -3792,7 +3812,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -3827,7 +3847,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>2020</v>
       </c>
@@ -3862,7 +3882,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>2020</v>
       </c>
@@ -3897,7 +3917,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>2021</v>
       </c>
@@ -3932,7 +3952,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>2021</v>
       </c>
@@ -3967,7 +3987,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>2021</v>
       </c>
@@ -4002,7 +4022,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>2021</v>
       </c>
@@ -4037,7 +4057,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>2021</v>
       </c>
@@ -4072,7 +4092,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>2021</v>
       </c>
@@ -4107,7 +4127,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>2021</v>
       </c>
@@ -4142,7 +4162,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>2021</v>
       </c>
@@ -4177,7 +4197,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>2021</v>
       </c>
@@ -4212,7 +4232,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>2021</v>
       </c>
@@ -4247,7 +4267,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>2021</v>
       </c>
@@ -4282,7 +4302,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>2021</v>
       </c>
@@ -4317,7 +4337,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>2021</v>
       </c>
@@ -4352,7 +4372,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>2021</v>
       </c>
@@ -4387,7 +4407,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>2021</v>
       </c>
@@ -4422,7 +4442,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>2021</v>
       </c>
@@ -4457,7 +4477,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>2021</v>
       </c>
@@ -4492,7 +4512,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>2022</v>
       </c>
@@ -4527,7 +4547,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>2022</v>
       </c>
@@ -4562,7 +4582,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>2022</v>
       </c>
@@ -4597,7 +4617,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>2022</v>
       </c>
@@ -4632,7 +4652,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>2022</v>
       </c>
@@ -4667,7 +4687,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>2022</v>
       </c>
@@ -4702,7 +4722,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>2022</v>
       </c>
@@ -4737,7 +4757,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>2022</v>
       </c>
@@ -4772,7 +4792,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>2022</v>
       </c>
@@ -4807,7 +4827,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>2022</v>
       </c>
@@ -4842,7 +4862,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>2022</v>
       </c>
@@ -4877,7 +4897,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>2022</v>
       </c>
@@ -4912,7 +4932,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>2022</v>
       </c>
@@ -4947,7 +4967,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>2022</v>
       </c>
@@ -4982,7 +5002,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>2022</v>
       </c>
@@ -5017,7 +5037,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>2022</v>
       </c>
@@ -5052,7 +5072,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>2022</v>
       </c>
@@ -5087,7 +5107,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>2022</v>
       </c>
@@ -5122,7 +5142,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>2022</v>
       </c>
@@ -5157,7 +5177,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>2022</v>
       </c>
@@ -5192,7 +5212,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>2022</v>
       </c>
@@ -5227,7 +5247,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>2022</v>
       </c>
@@ -5262,7 +5282,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>2022</v>
       </c>
@@ -5297,7 +5317,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>2022</v>
       </c>
@@ -5332,7 +5352,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>2023</v>
       </c>
@@ -5367,7 +5387,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>2023</v>
       </c>
@@ -5402,7 +5422,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>2023</v>
       </c>
@@ -5437,7 +5457,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>2023</v>
       </c>
@@ -5472,7 +5492,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>2023</v>
       </c>
@@ -5507,7 +5527,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -5542,7 +5562,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>2023</v>
       </c>
@@ -5577,7 +5597,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A102">
         <v>2023</v>
       </c>
@@ -5612,7 +5632,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A103">
         <v>2023</v>
       </c>
@@ -5647,7 +5667,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A104">
         <v>2023</v>
       </c>
@@ -5682,7 +5702,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A105">
         <v>2023</v>
       </c>
@@ -5717,7 +5737,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A106">
         <v>2023</v>
       </c>
@@ -5752,7 +5772,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A107">
         <v>2023</v>
       </c>
@@ -5787,7 +5807,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -5822,7 +5842,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A109">
         <v>2023</v>
       </c>
@@ -5857,7 +5877,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A110">
         <v>2023</v>
       </c>
@@ -5892,7 +5912,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>2023</v>
       </c>
@@ -5927,7 +5947,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>2023</v>
       </c>
@@ -5962,7 +5982,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A113">
         <v>2023</v>
       </c>
@@ -5997,7 +6017,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A114">
         <v>2023</v>
       </c>
@@ -6032,7 +6052,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A115">
         <v>2023</v>
       </c>
@@ -6067,7 +6087,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>2023</v>
       </c>
@@ -6102,7 +6122,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A117">
         <v>2024</v>
       </c>
@@ -6137,7 +6157,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A118">
         <v>2024</v>
       </c>
@@ -6172,7 +6192,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A119">
         <v>2024</v>
       </c>
@@ -6207,7 +6227,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A120">
         <v>2024</v>
       </c>
@@ -6242,7 +6262,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A121">
         <v>2024</v>
       </c>
@@ -6277,7 +6297,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A122">
         <v>2024</v>
       </c>
@@ -6312,7 +6332,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A123">
         <v>2025</v>
       </c>
@@ -6347,7 +6367,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A124">
         <v>2025</v>
       </c>
@@ -6382,7 +6402,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A125">
         <v>2025</v>
       </c>
@@ -6417,7 +6437,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A126">
         <v>2025</v>
       </c>
@@ -6452,7 +6472,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A127">
         <v>2025</v>
       </c>
